--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -2154,6 +2154,7 @@
 本機現況(2026-08-04 實測)：1006 只註冊在 SV 命名空間，可由 S1F3 與報表讀取，未註冊為 EC。⚠ 其回值的定義請一併注意：批已開時回閂鎖的作用中批號，批未開時回主畫面批號輸入欄當下的文字。貴端若對本機送 S2F15 ECID 1006：機台閒置時回 EAC=1(非可寫常數)、運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況該批號字串都直接丟棄 —— 不寫入任何欄位、不改變 SVID 1006 的回值、不發 CEID 48。
 ⚠ 請一併注意封包形狀的問題：貴端 2026-06-08 是把 1006 與 1007 包在同一個 S2F15 裡，該形狀在本機會造成「1007 寫入成功、整包卻回 EAC=1 且不發事件」(見本版第 22 項)。
 HT-90XX 的作法(供對照)：其 ECID 1006 綁在機台的系統批號輸入欄，寫入即成為機台的批號身分(UPH 檔名、2D 分選清單檔名、送測試機的 INNER_LOT_ID 皆取自該欄)；寫入不受 GEM 控制狀態限制，但整包 S2F15 在「機內有 IC」時一律回 EAC=2 且完全不寫入。另請注意 9045 另有獨立的客戶批號欄位，該欄位不在 SECS 上 —— ECID 1006 寫的是系統批號，不是客戶批號。
+⚠ 另有一處需請貴端一併確認：貴端提供的 SECS 規格書(SECS_20240826.xlsx「SV &amp; EC」)中，1006 這一列的機種支援欄是空白的(1007、1501、2758-2763、16000/16002/16023/16026、35011、37007 都標 V)，也就是規格書本身並未把 1006 列為 HT-90XX 家族支援的號碼；但兩棵 HT-90XX 原始碼都確實登錄了它，且貴端 host 當天也真的寫了三次。請一併釐清以哪一份為準。
 請貴端裁定四點：(a) 是否要求本機接受以 S2F15 ECID 1006 設定批號？(b) 若要，該值屬於哪一層批號身分？本機批號分兩層：機台身分批號(＝SVID 1006 回值、By Lot+Bin 分選的鍵、Soter 第 7 欄)與客戶批號(逐顆 IC 記錄、來源為貴端 WebAPI、Soter 第 6 欄)；單一 ASCII 值只能設定其中一層。(c) 寫入 1006 是否等同一次完整的批號宣告？本機「宣告批號」不只是存字串：會把該批加入登錄表(含容量與 2D 資料退役檢查)，開批時並向貴端 WebAPI 拉取該批的 2D→Bin 清單 —— 這是 2D 分選的前提。若 1006 只更新字串，機台會處於「批號顯示正確、但沒有分選資料」的狀態。(d) 寫入時機的閘門？比照 1007(運轉中亦可寫)，或比照 tray 幾何(僅 idle)？本方傾向僅在 idle 且機內無 IC 時受理。⚠ 附帶說明兩機的忙碌條件並不相同：HT-9046 只看「機內有無 IC」，本機另外還看「是否在運轉」，因此「已按 Start 但機內還沒有 IC」時本機會拒絕、HT-9046 會接受 —— 若貴端要求完全一致請一併告知。
 各答案的影響：回答「不需要」→ 本機維持 1006 可讀不可寫，批號一律走 RCMD SET_LOT_INFO(現行且已驗證的途徑)，請將 1006 自 S2F15 寫入清單移除，本機零改動。回答「需要」且指定為機台身分批號、等同完整宣告 → 本機將 1006 以 SV+EC 雙註冊(與 1007、1501、2758-2763 相同作法)，寫入時走與 SET_LOT_INFO 相同的登錄與 WebAPI 拉取流程，成功回 EAC=0 並發 CEID 48，空字串回 EAC=3。回答「需要」但只要更新顯示字串 → 可實作，但規格書必須明載「該寫入不建立批次、不拉 2D 資料、不影響分選」，⚠ 現場會有「批號看起來對了但分選資料沒進來」的風險，本方不建議。</t>
         </is>
@@ -10963,7 +10964,7 @@
       </c>
       <c r="F4" s="65" t="inlineStr">
         <is>
-          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。寫入成功回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC；空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
+          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。單獨送 1007 一筆且寫入成功時：回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC。⚠ 若與其他不可寫的號碼包在同一封包，值仍會寫入並存檔，但整包回非零 EAC 且不發 CEID 48(見下方註記與第 5 版第 22 項)；空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11370,7 @@
       </c>
       <c r="F21" s="65" t="inlineStr">
         <is>
-          <t>9045 的自動重測開關。HT-160S 只分選、不重測。</t>
+          <t>9045 的自動重測開關(其 SV 側另有 37009 USE AUTO RETEST)。HT-160S 不執行重測，機構上也沒有重測站；本機雖有逐顆的 RetestCode 欄位，但那是貴端 WebAPI 提供的資料、原樣寫入 Soter 輸出檔，機台不依它動作，因此本號碼在本機沒有可綁的對象。</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11400,7 @@
       </c>
       <c r="F22" s="65" t="inlineStr">
         <is>
-          <t>9045 為操作員在 Initial Start 輸入的進料匣盤數(Min 1 / Max 1000 / 預設 10)。本機的對應資料走另一個介面：AMR 交接時由 RCMD START_AGV 的 CP 參數 LOADERTRAYCOUNT 逐車宣告。⚠ 是否要另登錄為常數請見「Open item 10」。</t>
+          <t>9045 為操作員在 Initial Start 輸入的進料匣盤數(Min 1 / Max 1000 / 預設 10)。本機的對應資料走另一個介面：AMR 交接時由 RCMD START_AGV 的 CP 參數 LOADERTRAYCOUNT 逐車宣告，該值並以 SVID 38222 AMR Loader Tray Count 對外可讀。⚠ 是否要另登錄為常數請見「Open item 10」。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -1100,15 +1100,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="75" customHeight="1" s="8">
+    <row r="21" s="8">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>(2026-08-02 已回答，結論與原假設相反)2026-07-31 現場 log 證實貴端 host 確實會對 HT-160S 送 S2F33 / S2F35。且貴端的 S2F35 是「取代」而非「疊加」—— provision 完成後韌體預設的 Report 1 會從事件酬載中消失(當日 CEID 27 由 13 格有值退化為 1 格)，因此原本寫的「保留本機預設」不會發生。AMR 事件(CEID 272-275)在貴端自己的 RPTID 2000(7/7)與 2001(15/15)下覆蓋完整；需留意的是同時綁在這些事件上的 RPTID 502 本機目前只填得出 4 格(見下一列)。</t>
+      <c r="B21" s="57" t="inlineStr">
+        <is>
+          <t>(2026-08-02 已回答，結論與原假設相反)2026-07-31 現場 log 證實貴端 host 確實會對 HT-160S 送 S2F33 / S2F35。且貴端的 S2F35 是「取代」而非「疊加」—— provision 完成後韌體預設的 Report 1 會從事件酬載中消失(當日 CEID 27 由 13 格有值退化為 1 格)，因此原本寫的「保留本機預設」不會發生。AMR 事件(CEID 272-275)在貴端自己的 RPTID 2000(7/7)與 2001(15/15)下覆蓋完整；需留意的是同時綁在這些事件上的 RPTID 502，本機於 2026-08-02 當時只填得出 4 格〔20260804 更新：2026-08-03 補上 3 GemClock、1501 Setup File、1007 Operator ID 後已為 7/8，仍為空值的只剩 1513 Tester On/Off〕(見下一列)。</t>
         </is>
       </c>
     </row>
@@ -1486,9 +1486,9 @@
 • 1009 Lot Start Time — 'yyyy-mm-dd hh:nn:ss'(HT9045 線上格式)，本機開批時刻的唯一號碼。〔本版原保留同值的自有號碼 66033(斜線格式)，已於同日「追加項2」移除，請改讀 1009〕
 • 1103 / 1104 / 1105 Auto1-3 Count — 各 Auto 出料盤的放料數。
 • 1501 Setup File — 目前 recipe 名。註：同號的 ECID 1501 一直存在，但 SECS-II 的 SVID 與 ECID 是兩個獨立命名空間，而貴端是以 SVID 路徑讀它，故先前回空。本版在 SV 側補註冊同號、同型別、指向同一份資料。
-• 2758-2763 Type 1 Tray 幾何(Pitch X/Y、Start X/Y、Division X/Y) — 同 1501 的情況(原僅存在於 EC 側)。單位為 mm，與 HT9045 一致。
+• 2758-2763 Type 1 Tray 幾何(Pitch X/Y、Start X/Y、Division X/Y) — 同 1501 的情況(原僅存在於 EC 側)。〔20260804 更正：型別與單位逐項比對 HT9045 後一致 —— 2758 / 2759 Pitch 與 2760 / 2761 Start 為 F8、單位 mm；2762 / 2763 Division 為 I4、無單位(每列 / 每欄格數，S1F12 與 S2F30 的 UNITS 欄皆回零長度)。原句「單位為 mm」只適用於前四個。詳見「ECID」工作表。〕
 • 1259 / 1260 / 1261 Auto4-6 Count — 各 Auto 出料盤的放料數(見第 4 項)。〔本版原將這三站放在本機自有段 66025-66027，已於同日「追加項5」改用 HT-9011UC V3.33.899 的家族編號，請改讀 1259 / 1260 / 1261〕〔本版原另新增 66022-66024 Auto1-3 Count，已於同日「追加項2」移除 —— 與 1103-1105 同值，請改讀 1103 / 1104 / 1105，詳見該節〕
-〔20260804 更正：本項寫「共註冊 77 個 SVID」，該數字在任何時點都不曾成立 —— 同日「追加項」再加 SVID 4 / 9 後為 79，「追加項2」移除 4 個後為 75，「追加項4」加 1007 後為 76，「追加項5」為兩批各減 3 加 3、仍為 76。以 2026-08-04 實測 S1F11 &lt;L[0]&gt; 為準：76 個。〕</t>
+〔20260804 更新：本項的「共註冊 77 個 SVID(前版 58)」在第 4 版當時是正確的實測值(依據韌體即上方 commit 21d86f2)，需要更新的是它已不是現況。其後同日變動為：「追加項」新增 SVID 4 / 9 後為 79 個、「追加項2」移除 66022-66024 / 66033 後為 75 個、「追加項4」新增 1007 後為 76 個、「追加項5」Auto4-6 改號為兩批各減 3 加 3、仍為 76 個。以 2026-08-04 對實機實測的 S1F11 → S1F12 名稱表為準：現為 76 個，即本檔 SVID 工作表的 76 列。各版的數字一律以該版自身的「依據韌體」欄為基準，本檔 SVID 工作表則一律為當下實際註冊內容。〕</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       <c r="B59" s="39" t="inlineStr">
         <is>
           <t>已解決。貴端截圖中的 RPTID 502 = {1006, 1007, 1011, 3, 1501, 1517, 1518, 1513}，2026-07-31 當天本機只答得出第 7 格(1518 Real/Dummy = I4 2)，其餘 7 格皆為空 item —— 與截圖完全一致。
-本版起 502 的 8 格中有 6 格有值：1006 批號、1011 機況文字、3 設備時鐘、1501 recipe 名、1517 Start Mode、1518 Real/Dummy。已以 headless SECS host 對實際韌體實測確認。
+本版起 502 的 8 格中有 6 格可提供資料：1006 批號、1011 機況文字、3 設備時鐘、1501 recipe 名、1517 Start Mode、1518 Real/Dummy。已以 headless SECS host 對實際韌體實測確認這 6 格不再回空 item。⚠〔20260804 補充〕其中 1006 的值以「批號存在」為前提(定義同 Open item 9)：批已開時回閂鎖的作用中批號，批未開時回主畫面批號輸入欄當下的文字，兩者皆空時仍回零長度 —— 2026-08-04 機台閒置未開批的實測即為空值。因此下列兩個時點的 CEID 27 仍會帶空批號：(a) 開機後、批號尚未宣告之前；(b) 每次 Lot End 之後、下一批宣告之前(含貴端下 RCMD CLEAR_LOT_INFO 的情況)。若貴端要求這些時點也要有批號，請先下 RCMD SET_LOT_INFO 宣告，本機收到後即填入批號欄、1006 隨即有值，不需等 LOTSTART。1011 機況文字不受此限：發射 CEID 27 的判斷與 1011 的更新是同一個寫入點，故每一筆 CEID 27 一定帶當下的機況文字。
 剩下 2 格中，1007 Operator ID 已於同日「追加項4」實作(見本表末)〔20260804 更正：原文誤寫為「追加項3」，追加項3 是 CEID 字典補齊至 292 與 CEID 272-275 名稱更正，不含 1007〕，⚠ 本項原先建議貴端自報表定義中移除 1007，該建議作廢，請保留。真正給不出來的只有 1513 Tester On/Off(本機為 Tray Sorter，無測試機)，建議自報表定義中移除。
 同一封信的另一張截圖 RPTID 501 = {1101, 1102, 1103-1108, 16296-16299} 全空，本版起 12 格中有 5 格有值(1101 Loader Count、1102 Output Total、1103-1105 Auto1-3)；其餘見第 4、5 項。</t>
         </is>
@@ -2044,7 +2044,8 @@
       </c>
       <c r="B107" s="61" t="inlineStr">
         <is>
-          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor(內容同第 4 版 追加項5；本版未改任何韌體程式碼，純為文件補齊與更正)。本版所有數字係以 headless SECS host 對實際韌體(EXE\ht160s.exe)實測回覆為準，非由原始碼推算。</t>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (commit 8bf575c)。本版文件本身未修改任何一行韌體程式碼，SECS/GEM 相關程式檔自第 4 版 追加項5 起亦完全未動。惟韌體樹在 追加項5(commit c7307bf，2026-08-03 22:07)之後另有五筆進入建置的變更：TrayArm 空盤取放最佳化(0bd60aa)、TrayArm 晚期改道改為依種類詢問(a1ddb7d)、SecsGem 程式內註解更正(aee6725，逐行查證為純註解、無行為變更)、TrayArm 註解更正(b577c7e，同上)、Auto 前升盤等待補上逾時(8bf575c)。本版所有數字係以 headless SECS host 對「與 8bf575c 同內容」的建置(EXE\ht160s.exe，2026-08-04 09:12 建置；該修正於同日 09:13 提交)實測回覆為準，非由原始碼推算。
+⚠ 上述四筆中只有 8bf575c 會改變線上訊息：出料放盤路徑上，Auto 前升盤汽缸(C_Auto1~6_FrontRiseTray)的「上升」動作若 5 秒內未到位，改為發出汽缸警報(ALCD=4 的 4xxxx 碼，均已列於本檔「ALID」工作表)，貴端因此會收到一筆先前不會出現的 S5F1；先前為無聲卡死 —— 機台端僅留下 State Record 快照，線上不發任何訊息。host 端無需修改對照表(該 ALID 已在目錄內)。⚠ 此項尚待上機以實際 reed 驗證。⚠ 未涵蓋範圍：同一汽缸的「下降」動作與批末 Clean Out 路徑的六支前升盤目前仍為無逾時等待，卡住時仍不發警報，本方已列入後續修正。</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2069,7 @@
       </c>
       <c r="B109" s="61" t="inlineStr">
         <is>
-          <t>本檔原先只寫「警報目錄目前 481 筆」而沒有清單。本版新增第 6 張工作表「ALID」，列出全部 481 筆的 ALID / 警報碼 / ALCD / 類別 / 訊息原文，順序與 S5F6 回覆完全相同。ALID = 警報碼字串的 31 進位多項式雜湊(unsigned 32-bit)，以 UINT_4 送出，S5F1 與 S5F6/S5F8 共用同一個雜湊，故同一支警報在事件與目錄中的 ALID 恆等。⚠ 有 14 筆超過 2^31-1(JAM 家族，最大 3184282107)，請以無號 32 位元解析。⚠ ALCD 是本機自有的警報分類(0=Jam / 1=Message / 4=汽缸 / 5=馬達 / 6=真空 / 8=其他警示)，不是 SEMI E5 的標準類別編碼，且不能從警報碼前綴推導(例如 WAR0962 的 ALCD 是 1 而非 8)，請以本表的 ALCD 欄為準。</t>
+          <t>本檔原先只寫「警報目錄目前 481 筆」而沒有清單。本版新增第 6 張工作表「ALID」，列出全部 481 筆的 ALID / 警報碼 / ALCD / 類別 / 訊息原文，順序與 S5F6 回覆完全相同。ALID = 警報碼字串的 31 進位多項式雜湊(unsigned 32-bit)，以 UINT_4 送出，S5F1 與 S5F6/S5F8 共用同一個雜湊，故同一支警報在事件與目錄中的 ALID 恆等。⚠ 有 14 筆超過 2^31-1(JAM 家族，最大 3184282107)，請以無號 32 位元解析。⚠ ALCD 是本機自有的警報分類(0=Jam / 1=Message / 4=汽缸 / 5=馬達 / 6=真空 / 8=其他警示)，不是 SEMI E5 的標準類別編碼，且不能從警報碼前綴推導(例如 WAR0962 的 ALCD 是 1 而非 8)，請以本表的 ALCD 欄為準。⚠ 兩點請務必併同實作(詳見該工作表表頭)：(a) S5F1 事件的 ALCD 不帶類別(發生 0x80 / 解除 0x00，低 7 位恆為 0)，與 HT-9046 不同，要分類請以 ALID 查本目錄；(b) 有兩類警報的 ALID 不在目錄內 —— 吸嘴真空家族的 12 個 SUC 字串碼(目錄裡的 60000-60005 實機不會送)與尚未登錄成警報碼的自由字串警報，host 端請保留「未知 ALID 就顯示 ALTX 原文」的 fallback。本方已將兩者的代碼一致性列入後續收斂項目。</t>
         </is>
       </c>
     </row>
@@ -2085,17 +2086,18 @@
       </c>
     </row>
     <row r="111" s="8">
-      <c r="A111" s="60" t="inlineStr">
-        <is>
-          <t>⚠ 22. 新發現缺陷：S2F15 混合封包「部分成功卻回報失敗」(本方待修)</t>
+      <c r="A111" s="61" t="inlineStr">
+        <is>
+          <t>⚠ 22. 新發現缺陷：S2F15 的兩個寫入缺陷(本方待修)</t>
         </is>
       </c>
       <c r="B111" s="61" t="inlineStr">
         <is>
           <t>以貴端 2026-06-08 對 HT-9046 送的封包形狀 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 對本機實測(2026-08-04)：本機逐筆套用 —— 1006 不可寫使整包 EAC 變成 1，但 1007 的值已實際寫入並存檔(S2F13 讀回為新值、主畫面同步更新)，且因為 CEID 48 的發射條件是 EAC==0，該次變更不會發事件。也就是「機台已經改了、卻回報失敗、也不通知」。HT-9046 沒有這個現象：它的忙碌閘是整包擋在任何寫入之前。
-同一現象在機台忙碌時也成立：此時 1006 讓整包 EAC 變成 2，但 1007 的處理在忙碌閘之前，仍然寫入。另外，貴端當天 17:51:58 還有一筆是 L[2]{L[2]{1007,"AGV"},L[2]{37007,1}}，37007 本機亦未登錄，故該形狀也會踩到同一個現象 —— 問題不限於 1006。
-本方認定為缺陷，將於下一批次修正為「先整包檢查、全部可寫才逐筆套用」(對齊 HT9045)。⚠ 在修正版交機之前，請讓每一個 S2F15 封包只包含本機可寫的號碼(1007 或 2758-2763)；只要混入本機不可寫或未登錄的號碼，該封包內可寫的部分就會「已寫入卻回報失敗」。
-附帶提醒：貴端當天 24 筆 S2F15 所寫的號碼中，本機只登錄 1007 一個，因此同一份 host 設定打到本機時 24 筆都會回非零 EAC(其中 4 筆含 1007 者會實際寫入)。</t>
+依程式碼判讀，同一現象在機台忙碌時亦成立：此時 1006 讓整包 EAC 變成 2，但 1007 的處理排在忙碌閘之前，仍然寫入(⚠ 此點尚未實測，本版實測皆在機台閒置下進行 —— 見本表「驗證」第 3 點)。另外，貴端當天 17:51:58 還有一筆是 L[2]{L[2]{1007,"AGV"},L[2]{37007,1}}，37007 本機亦未登錄，故該形狀也會踩到同一個現象 —— 問題不限於 1006。
+本方認定為缺陷，將於下一批次修正為「先整包檢查、全部可寫才逐筆套用」(對齊 HT9045)。⚠ 在修正版交機之前，請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一包，不得混入本機不可寫或未登錄的號碼，並僅在機台閒置且機內無 IC 時送出。⚠ 「整包都是可寫的號碼」並不等於安全：運轉中送 {1007＋任一 tray 幾何} 時 1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進配方檔 —— 被靜默改動的是會影響取放座標的機構參數。成因是持久化與事件的判斷條件不同：寫入與存檔只看「該筆是否寫成功」，而 CEID 48 只在整包 EAC=0 時才發。
+附帶提醒：貴端當天 24 筆 S2F15 所寫的號碼中，本機只登錄 1007 一個，因此同一份 host 設定打到本機時 24 筆都會回非零 EAC(其中 4 筆含 1007 者會實際寫入)。
+⚠ 缺陷二(2026-08-04 同時發現，程式碼查證)：S2F15 的 ECV 型別解析不完整。本機的 ECV 只認 ASCII 與 U1/U2/U4/I1/I2/I4；F4 / F8 / BOOLEAN / BINARY / U8 / I8 一律不解析，而且不是回錯誤 —— 取到空字串後當 0 寫入、存進當前配方的 setup.ini，並仍回 EAC=0 且照發 CEID 48。也就是 host 以合乎規格的 &lt;F8 102.5&gt; 寫 ECID 2760，會得到「完全成功」的回覆而 tray 起始位置被歸零。⚠ HT-9046 的 S2F15 有 F4/F8 的解析分支，貴端若沿用 9046 的寫入程式碼打到本機就會踩到。過渡辦法：ECV 一律以 ASCII 送(例 &lt;L,2 &lt;U4 2760&gt; &lt;A '102.5'&gt;&gt;)。本方將於下一批次改為「依該 EC 宣告的型別解析；不認得的型別回 EAC=1 並記錄，絕不以 0 代替」。</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2121,7 @@
       </c>
       <c r="B113" s="61" t="inlineStr">
         <is>
-          <t>檔首「本次修訂內容」「尚待貴端確認」兩區塊是就地維護的現況清單，仍留有第 1 版與 8/2 的數字，已逐格補上 20260804 現況：SVID 51→76、CEID 1-275→1-292、發射點 52→56+1(合計 57)、未發射 223→235、RPTID 502 由 4/8→7/8、501 由 2/12→5/12、508 由 1/6→2/6、502 仍為空的只剩 1513。另更正三處版內錯誤：第 4 版第 1 項的「77 個 SVID」(任何時點都不曾成立)、第 4 版第 3 項誤寫 1007 由「追加項3」實作(實為追加項4)、追加項4「本次未變動」誤列 S2F29/S2F30 回覆形狀未變(實際由 L,7 變 L,8)。圖例的「淡黃底＝本次修訂變更的儲存格」也已更正為累計標示。</t>
+          <t>檔首「本次修訂內容」「尚待貴端確認」兩區塊是就地維護的現況清單，仍留有第 1 版與 8/2 的數字，已逐格補上 20260804 現況：SVID 51→76、CEID 1-275→1-292、發射點 52→56+1(合計 57)、未發射 223→235、RPTID 502 由 4/8→7/8、501 由 2/12→5/12、508 由 1/6→2/6、502 仍為空的只剩 1513。另更正兩處版內錯誤：第 4 版第 3 項誤寫 1007 由「追加項3」實作(實為追加項4)、追加項4「本次未變動」誤列 S2F29/S2F30 回覆形狀未變(實際由 L,7 變 L,8)。並補註兩處過時 / 不精確之處：第 4 版第 1 項的「77 個 SVID」在該版依據韌體(commit 21d86f2)當時正確、現況為 76 個，已於該格加註沿革；同項的 tray 幾何「單位為 mm」只適用於 Pitch / Start 四個，Division X/Y 無單位，已加註更正。圖例的「淡黃底＝本次修訂變更的儲存格」也已更正為累計標示。</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2155,7 @@
           <t>**ECID 1006 Lot ID 是否開放貴端以 S2F15 寫入?**
 本機現況(2026-08-04 實測)：1006 只註冊在 SV 命名空間，可由 S1F3 與報表讀取，未註冊為 EC。⚠ 其回值的定義請一併注意：批已開時回閂鎖的作用中批號，批未開時回主畫面批號輸入欄當下的文字。貴端若對本機送 S2F15 ECID 1006：機台閒置時回 EAC=1(非可寫常數)、運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況該批號字串都直接丟棄 —— 不寫入任何欄位、不改變 SVID 1006 的回值、不發 CEID 48。
 ⚠ 請一併注意封包形狀的問題：貴端 2026-06-08 是把 1006 與 1007 包在同一個 S2F15 裡，該形狀在本機會造成「1007 寫入成功、整包卻回 EAC=1 且不發事件」(見本版第 22 項)。
-HT-90XX 的作法(供對照)：其 ECID 1006 綁在機台的系統批號輸入欄，寫入即成為機台的批號身分(UPH 檔名、2D 分選清單檔名、送測試機的 INNER_LOT_ID 皆取自該欄)；寫入不受 GEM 控制狀態限制，但整包 S2F15 在「機內有 IC」時一律回 EAC=2 且完全不寫入。另請注意 9045 另有獨立的客戶批號欄位，該欄位不在 SECS 上 —— ECID 1006 寫的是系統批號，不是客戶批號。
+HT-90XX 的作法(供對照)：其 ECID 1006 綁在機台的系統批號輸入欄，寫入即成為機台的批號身分(UPH 檔名、2D 分選清單檔名、送測試機的 INNER_LOT_ID 皆取自該欄)；寫入不受 GEM 控制狀態限制，但整包 S2F15 在「機內有 IC」時一律回 EAC=2 且完全不寫入。⚠ 另請注意 9045 的兩層批號在 SECS 上是「各用一個 ECID」，並非只有 1006：ECID 1006 寫的是系統批號，客戶批號另有 ECID 1583 Lot Information Customer Lot ID —— 貴端的 HT-9046LS 與 HT-9011UC 皆有登錄(以 S2F29 全查即可看到)，該值就是 9045 畫面上的客戶批號。另有 ECID 1582 Lot Information Inner Lot ID，但它是系統批號的鏡像，並非第三層批號。因此若貴端需要同時設定兩層批號，可比照 9045 各用一個號碼(1006 系統批號、1583 客戶批號)，不必把兩層批號擠在同一個 ECID —— 請於下列 (b) 一併裁定是否要求本機也登錄 1583(本機的客戶批號目前來源為貴端 WebAPI，逐顆 IC 記錄於 Soter 第 6 欄)。
 ⚠ 另有一處需請貴端一併確認：貴端提供的 SECS 規格書(SECS_20240826.xlsx「SV &amp; EC」)中，1006 這一列的機種支援欄是空白的(1007、1501、2758-2763、16000/16002/16023/16026、35011、37007 都標 V)，也就是規格書本身並未把 1006 列為 HT-90XX 家族支援的號碼；但兩棵 HT-90XX 原始碼都確實登錄了它，且貴端 host 當天也真的寫了三次。請一併釐清以哪一份為準。
 請貴端裁定四點：(a) 是否要求本機接受以 S2F15 ECID 1006 設定批號？(b) 若要，該值屬於哪一層批號身分？本機批號分兩層：機台身分批號(＝SVID 1006 回值、By Lot+Bin 分選的鍵、Soter 第 7 欄)與客戶批號(逐顆 IC 記錄、來源為貴端 WebAPI、Soter 第 6 欄)；單一 ASCII 值只能設定其中一層。(c) 寫入 1006 是否等同一次完整的批號宣告？本機「宣告批號」不只是存字串：會把該批加入登錄表(含容量與 2D 資料退役檢查)，開批時並向貴端 WebAPI 拉取該批的 2D→Bin 清單 —— 這是 2D 分選的前提。若 1006 只更新字串，機台會處於「批號顯示正確、但沒有分選資料」的狀態。(d) 寫入時機的閘門？比照 1007(運轉中亦可寫)，或比照 tray 幾何(僅 idle)？本方傾向僅在 idle 且機內無 IC 時受理。⚠ 附帶說明兩機的忙碌條件並不相同：HT-9046 只看「機內有無 IC」，本機另外還看「是否在運轉」，因此「已按 Start 但機內還沒有 IC」時本機會拒絕、HT-9046 會接受 —— 若貴端要求完全一致請一併告知。
 各答案的影響：回答「不需要」→ 本機維持 1006 可讀不可寫，批號一律走 RCMD SET_LOT_INFO(現行且已驗證的途徑)，請將 1006 自 S2F15 寫入清單移除，本機零改動。回答「需要」且指定為機台身分批號、等同完整宣告 → 本機將 1006 以 SV+EC 雙註冊(與 1007、1501、2758-2763 相同作法)，寫入時走與 SET_LOT_INFO 相同的登錄與 WebAPI 拉取流程，成功回 EAC=0 並發 CEID 48，空字串回 EAC=3。回答「需要」但只要更新顯示字串 → 可實作，但規格書必須明載「該寫入不建立批次、不拉 2D 資料、不影響分選」，⚠ 現場會有「批號看起來對了但分選資料沒進來」的風險，本方不建議。</t>
@@ -2182,7 +2184,7 @@
       </c>
       <c r="B118" s="61" t="inlineStr">
         <is>
-          <t>CEID 的編號、語意與發射點、SVID 的編號與名稱、預設 Report 1 的 13 個 SV 內容與順序、S1F23/S1F24 的回覆形狀、EC 可寫範圍、S5 警報目錄的內容與筆數、Soter 輸出檔契約 —— 全部未變。本版沒有修改任何一行韌體程式碼，機台行為與線上任何一筆訊息的內容、時序、形狀完全不變；本版只是把既有行為補寫進文件，並更正文件本身的過時敘述。</t>
+          <t>CEID 的編號、語意與發射點、SVID 的編號與名稱、預設 Report 1 的 13 個 SV 內容與順序、S1F23/S1F24 的回覆形狀、EC 可寫範圍、S5 警報目錄的內容與筆數、Soter 輸出檔契約 —— 全部未變。本版文件沒有修改任何一行韌體程式碼，SECS/GEM 程式檔自第 4 版 追加項5 起亦無任何行為變更，故既有事件與回覆的內容、順序、型別完全不變；本版只是把既有行為補寫進文件，並更正文件本身的過時敘述。⚠ 唯一的例外在機構層：韌體樹於 2026-08-04 另有一筆修正(commit 8bf575c)，使出料放盤路徑上卡住的 Auto 前升盤汽缸由「無聲等待」改為 5 秒後發出汽缸警報，貴端因此會在該故障情境下多收到一筆 S5F1(該 ALID 已在本檔「ALID」工作表內，host 端無需修改對照表)。詳見本版「依據韌體」欄的說明與未涵蓋範圍。</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2196,7 @@
       </c>
       <c r="B119" s="61" t="inlineStr">
         <is>
-          <t>1. 本版無程式碼變更，故不需重新建置(韌體同第 4 版 追加項5)。
+          <t>1. 本版文件無程式碼變更，故未重新建置；實測所用的韌體為 commit 8bf575c 的建置(EXE\ht160s.exe，2026-08-04 09:12) —— 不是 追加項5 的建置。兩者的 SECS/GEM 程式檔完全相同，故本檔所有 SECS 數字對兩個建置一致，差異僅在機構層(見「依據韌體」欄)。
 2. 以 headless SECS host 對實際韌體(EXE\ht160s.exe)做 HSMS round-trip 實測(2026-08-04 10:05 與 10:12)，本版新增的兩張表與所有更正的數字皆以實測回覆為依據：
 • S2F29 &lt;L[0]&gt; → S2F30 回 L,8(EC 目錄逐格記錄，即「ECID」工作表；註冊順序 1501、1007、2760、2758、2761、2759、2762、2763)；S2F13 &lt;L[0]&gt; → S2F14 回 8 個值，與名單順序一致。
 • S5F5 &lt;L[0]&gt; → S5F6 回 481 筆(34,662 bytes)；S5F7 → S5F8 亦為 481 筆(全目錄)。481 筆的警報碼、ALCD 與訊息與本機 system\AlarmList.csv 逐筆比對 481/481 相同，ALID 無重複。
@@ -2203,7 +2205,11 @@
 • ECID 1006：S2F15 寫入回 EAC=1，SVID 1006 的值不變 —— Open item 9 的現況以此實測為據。
 • 混合封包 L[2]{1006,1007}：回 EAC=1，但 1007 已寫入且無 CEID 48 —— 第 22 項的缺陷以此實測為據。
 • 未登錄的 ECID：S2F29 回 L,6 內名稱 / 三個界限 / 單位皆為零長度；S2F15 寫入回 EAC=1。
-3. ⚠ 尚未驗證：ECID 1007「運轉中亦可寫」本次是在機台閒置下實測的(程式碼層面 1007 的分支確實在忙碌閘之前，但運轉中的實機寫入尚未實測)；第 22 項的缺陷尚未修正；上機驗證待執行。</t>
+3. ⚠ 尚未驗證，逐項列明：
+• ECID 1007「運轉中亦可寫」本次是在機台閒置下實測的(程式碼層面 1007 的分支確實排在忙碌閘之前，但運轉中的實機寫入尚未實測)。
+• EAC=2(機台忙碌)本次亦未實測 —— 兩段實測皆在機台閒置下進行(ECID 1006 回 EAC=1 即為閒置之證；忙碌時同一筆會回 EAC=2)。
+• tray 幾何 2758-2763 的 S2F15 寫入本次完全未實測 —— 兩段 round-trip 只對 ECID 1007、1006、16000 送過 S2F15，2758-2763 僅有讀取(S2F13/S2F14、S1F3/S1F4、S2F29/S2F30)。故下列三項目前僅為程式碼查證：idle 閘的實際擋阻、無法解出數值的 ECV 會被當 0 寫入並存進配方檔(且仍回 EAC=0 並發 CEID 48)、以及本機實際可接受的 ECV 型別範圍(第 22 項第二個缺陷)。本方將於下一批次補測並回報。
+• 第 22 項的兩個缺陷尚未修正；8bf575c 的汽缸逾時尚待上機以實際 reed 驗證；整體上機驗證待執行。</t>
         </is>
       </c>
     </row>
@@ -2514,9 +2520,9 @@
     &gt;
   &gt;
 .
-[20260804] 已實作。可寫的 EC 只有兩組：ECID 1007 Operator ID(不受 idle 閘，運轉中亦可寫)與 2758-2763 Tray 幾何(僅機台閒置且機內無 IC 時受理)。其餘號碼(含已登錄但唯讀的 1501)一律回 EAC=1。EAC：0=全部受理 / 1=封包格式錯誤或含不可寫的號碼 / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。
-⚠ 混合封包請拆開送(2026-08-04 實測)。S2F16 的 EAC 是「整包一個值」，而本機是逐筆套用。以貴端 2026-06-08 對 HT-9046 送的同一種封包 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 實測本機：1007 的值確實已寫入並存檔(可由 S2F13 讀回)，但整包回 EAC=1、且不發 CEID 48 —— 「部分成功卻回報失敗」。HT-9046 不會如此(它的忙碌閘是整包擋在寫入之前)。同一現象在機台忙碌時也會發生(此時整包回 EAC=2，1007 仍已寫入 —— 因為 1007 的處理在忙碌閘之前)。貴端當天另有一筆是把 1007 與 37007 包在一起，37007 本機同樣未登錄，故該形狀也會踩到同一個現象。本方已列為缺陷待修(見「2026-08-04 第 5 版修訂」第 22 項)；在修好之前，⚠ 請讓每一個 S2F15 封包只包含本機可寫的號碼(1007 或 2758-2763) —— 只要同一封包內混入任何本機不可寫或未登錄的號碼(1006、37007、16000、16002、16023、16026、35011 等)，就會出現這個現象。
-⚠ 另請注意：S2F30 回報的 ECMIN / ECMAX 目前是零長度(未宣告，與 HT9045 相同)，寫入路徑也不做數值範圍檢查；tray 幾何若收到非數值字串會被當 0 寫入並存進配方檔，請勿送非數值。</t>
+[20260804] 已實作。可寫的 EC 只有兩組：ECID 1007 Operator ID(不受 idle 閘，運轉中亦可寫)與 2758-2763 Tray 幾何(僅機台閒置且機內無 IC 時受理)。其餘號碼(含已登錄但唯讀的 1501)一律不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)。⚠ 忙碌閘排在號碼判定之前，故 EAC=2 只代表當下忙碌、不代表該號碼可寫 —— 對本機不可寫或未登錄的號碼，閒下來再送只會由 2 改成 1，永遠不會成功。EAC：0=全部受理 / 1=封包格式錯誤或含不可寫的號碼 / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。
+⚠ 混合封包請拆開送(2026-08-04 實測)。S2F16 的 EAC 是「整包一個值」，而本機是逐筆套用。以貴端 2026-06-08 對 HT-9046 送的同一種封包 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 實測本機：1007 的值確實已寫入並存檔(可由 S2F13 讀回)，但整包回 EAC=1、且不發 CEID 48 —— 「部分成功卻回報失敗」。HT-9046 不會如此(它的忙碌閘是整包擋在寫入之前)。依程式碼判讀，同一現象在機台忙碌時亦會發生(此時整包回 EAC=2，1007 仍已寫入 —— 因為 1007 的處理排在忙碌閘之前)；⚠ 此忙碌情形尚未實測，2026-08-04 的實測全部在機台閒置下進行(實得 EAC 僅 0 / 1 / 3)，本方將於上機驗證時補齊。貴端當天另有一筆是把 1007 與 37007 包在一起，37007 本機同樣未登錄，故該形狀也會踩到同一個現象。本方已列為缺陷待修(見「2026-08-04 第 5 版修訂」第 22 項)；在修好之前，⚠ 請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成為一個封包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一個封包，不得混入本機不可寫或未登錄的號碼(1501、1006、37007、16000、16002、16023、16026、35011 等)，並僅在機台閒置且機內無 IC 時送出。⚠ 特別提醒：「整包都是可寫的號碼」並不等於安全 —— 因為 1007 排在忙碌閘之前，運轉中送 {1007＋任一 tray 幾何} 時，1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2 且不發事件；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進當前配方檔(存檔只看該筆是否寫成功，不看 EAC)。原則：一個封包只放一個號碼最安全，最低限度是 1007 絕不與其他號碼同包。不含 1007 的純 tray 幾何封包是全有全無(忙碌時整包拒絕、閒置時整包寫入並發 CEID 48)，可安全合併。
+⚠ 另請注意：S2F30 回報的 ECMIN / ECMAX 目前是零長度(未宣告，與 HT9045 相同)，寫入路徑也不做數值範圍檢查；tray 幾何若無法解出數值就會被當 0 寫入並存進配方檔。⚠ 這不只發生在非數值字串 —— 以 F4 / F8 item 送出的「合法數值」在本機同樣解不出來，會被當 0 寫入卻仍回 EAC=0 並發 CEID 48(HT-9046 的 S2F15 有 F4/F8 分支，本機沒有，貴端若沿用 9046 的寫入程式碼會踩到)。請一律以 ASCII 送 ECV，並勿送非數值。詳見「ECID」工作表第 (5) 點。</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2689,7 @@
       <c r="E16" s="14" t="inlineStr">
         <is>
           <t>[20260729] 已實作。警報發生/解除各送一次；ALCD bit7 0x80=set / 0x00=clear，ALID 由警報碼雜湊產生(與 S5F6/S5F8 目錄同一來源)。
-[20260804] 補充 ALID 的產生方式與目錄：ALID = 警報碼字串的 31 進位多項式雜湊(alid = alid*31 + 每個字元，unsigned 32-bit)，以 UINT_4 送出。⚠ 481 筆中有 14 筆超過 2^31-1(JAM 家族，最大 3184282107)，host 端請以「無號 32 位元」解析，存進有號整數會變負數。S5F1 與 S5F6/S5F8 共用同一個雜湊，故同一支警報在事件與目錄中的 ALID 恆等。完整目錄已列於本檔新增的「ALID」工作表(第 6 張)。⚠ 例外：少數尚未登錄成警報碼的自由字串警報(例如安全門 / 緊急停止 / 馬達超程等)其 ALID 為該字串本身的雜湊，不在目錄內、也可能隨字串修訂而改變；本方已列入後續收斂項目。</t>
+[20260804] 補充 ALID 的產生方式與目錄：ALID = 警報碼字串的 31 進位多項式雜湊(alid = alid*31 + 每個字元，unsigned 32-bit)，以 UINT_4 送出。⚠ 481 筆中有 14 筆超過 2^31-1(JAM 家族，最大 3184282107)，host 端請以「無號 32 位元」解析，存進有號整數會變負數。S5F1 與 S5F6/S5F8 共用同一個雜湊，故同一支警報在事件與目錄中的 ALID 恆等。完整目錄已列於本檔新增的「ALID」工作表(第 6 張)。⚠ 例外(請務必看「ALID」工作表表頭的完整說明)：兩類警報的 ALID 不在目錄內 —— (1) 吸嘴真空家族以字串碼 SUC&lt;吸嘴索引&gt;&lt;錯誤別&gt; 上報(共 12 個，目錄裡的 60000-60005 實機不會送)；(2) 尚未登錄成警報碼的自由字串警報(安全門 / 緊急停止 / 馬達電源 / 氣壓 / 離子風扇、各軸馬達超程的 &lt;軸別&gt;_MotOverLimitErr、部分英文長句警報)，其 ALID 為字串雜湊、會隨字串修訂而改變，其中一支還隨介面語言改變。host 端請保留「未知 ALID 就顯示 ALTX 原文」的 fallback。⚠ 另請注意 S5F1 的 ALCD 不帶類別(發生 0x80 / 解除 0x00，低 7 位恆為 0)，要分類請以 ALID 查「ALID」工作表。本方已將代碼一致性列入後續收斂項目。</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2751,7 @@
   &gt;
 .
 [20260802] 已實作，但不支援 ALID 過濾：不論請求帶不帶 ALID 清單，S5F6 一律回完整警報目錄，建議直接送 &lt;L[0]&gt; 全查。目錄由本機警報碼 SSOT 即時產生，目前 481 筆(2026-07-20 移除 16 支機構上未安裝的汽缸，對應 96 個 4xxxx 汽缸碼)。〔20260804 更正：原文「筆數會隨機構配置增減」不正確 —— 目錄由程式在開機時固定建成，不受 General.ini、IO 表、AMR 開關或模擬模式影響，同一版韌體恆為 481 筆；只有機構增減汽缸 / 馬達數量(需改程式)才會變動。本次已以實測確認：S5F6 = 481 筆、S5F8 = 481 筆，與本機 system\AlarmList.csv 的 481 筆逐筆相同。〕S5F7/S5F8 行為相同 —— 本機無 per-ALID 啟用表，「已啟用清單」恆等於全目錄。
-[20260804] 全部 481 筆的 ALID / 警報碼 / ALCD / 訊息已列於本檔新增的「ALID」工作表(第 6 張)，內容即 2026-08-04 實測 S5F6 回覆的逐筆記錄(順序亦與回覆相同)，可直接用於 host 端建表。</t>
+[20260804] 全部 481 筆的 ALID / 警報碼 / ALCD / 訊息已列於本檔新增的「ALID」工作表(第 6 張)，內容即 2026-08-04 實測 S5F6 回覆的逐筆記錄(順序亦與回覆相同)，可用於 host 端建表；⚠ 但請併同「ALID」工作表表頭第 4 段的兩個例外家族與「未知 ALID 顯示 ALTX」的 fallback 一起實作。</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10868,7 @@
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="1"/>
     <col width="30" customWidth="1" style="8" min="2" max="2"/>
-    <col width="8" customWidth="1" style="8" min="3" max="3"/>
+    <col width="22" customWidth="1" style="8" min="3" max="3"/>
     <col width="8" customWidth="1" style="8" min="4" max="4"/>
     <col width="20" customWidth="1" style="8" min="5" max="5"/>
     <col width="96" customWidth="1" style="8" min="6" max="6"/>
@@ -10889,7 +10895,8 @@
       </c>
       <c r="C2" s="63" t="inlineStr">
         <is>
-          <t>型別</t>
+          <t>型別
+(本機宣告；S2F14 / S2F30 以此編碼，非 S2F15 寫入用的 item 型別 —— 見第 (5) 點)</t>
         </is>
       </c>
       <c r="D2" s="63" t="inlineStr">
@@ -10934,7 +10941,7 @@
       </c>
       <c r="F3" s="65" t="inlineStr">
         <is>
-          <t>目前配方(Setup File)名。⚠ SV 側同號的名稱是 Setup File(與 HT-90XX 一致)，EC 側目前回 Recipe Name，本方擬於下一批次對齊(見第 5 版第 23 項)。S2F15 寫入回 EAC=1。</t>
+          <t>目前配方(Setup File)名。⚠ SV 側同號的名稱是 Setup File(與 HT-90XX 一致)，EC 側目前回 Recipe Name，本方擬於下一批次對齊(見第 5 版第 23 項)。S2F15 寫入不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況都不寫入，EAC=2 不表示稍後重送會成功。</t>
         </is>
       </c>
     </row>
@@ -10959,12 +10966,12 @@
       </c>
       <c r="E4" s="65" t="inlineStr">
         <is>
-          <t>可寫(運轉中亦可)</t>
+          <t>可寫(運轉中亦可 —— 依程式碼，運轉中尚未實測)</t>
         </is>
       </c>
       <c r="F4" s="65" t="inlineStr">
         <is>
-          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。單獨送 1007 一筆且寫入成功時：回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC。⚠ 若與其他不可寫的號碼包在同一封包，值仍會寫入並存檔，但整包回非零 EAC 且不發 CEID 48(見下方註記與第 5 版第 22 項)；空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
+          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入(此點為程式碼判讀，運轉中的實機寫入尚未實測，見第 5 版「驗證」第 3 點)，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。單獨送 1007 一筆且寫入成功時：回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC。⚠ 若與其他不可寫的號碼包在同一封包，值仍會寫入並存檔，但整包回非零 EAC 且不發 CEID 48(見下方註記與第 5 版第 22 項)；空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
         </is>
       </c>
     </row>
@@ -11148,17 +11155,22 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="8">
       <c r="A12" s="61" t="inlineStr">
         <is>
-          <t>⚠ 讀取與寫入的四個實務要點(2026-08-04 實測)：(1) S2F13/S2F29 送 &lt;L[0]&gt; 全查時，回覆順序是本機的「註冊順序」1501、1007、2760、2758、2761、2759、2762、2763 —— 不是號碼遞增，且 Start 與 Pitch 是交錯的；S2F14 依 SEMI E5 不回 ECID(酬載為 L,n{ECV})，請以請求順序對位取值。(2) EAC：0=全部受理 / 1=格式錯誤或含不可寫號碼(含唯讀的 1501 與所有未登錄號碼) / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。⚠ 非零的 EAC 不代表整包都沒生效 —— 本機逐筆套用：封包內若混入不可寫或未登錄的號碼，可寫的那幾筆仍會實際寫入並存檔，但整包回非零 EAC(閒置時 1、忙碌時 2)且不發 CEID 48，即「部分成功卻回報失敗」。詳見「2026-08-04 第 5 版修訂」第 22 項；本方待修，修好前請讓每個封包只包含可寫的號碼(1007 或 2758-2763)。(3) S2F30 回報的 ECMIN / ECMAX 為零長度(未宣告，與 HT-90XX 相同)，寫入路徑也不做範圍檢查；tray 幾何若收到非數值字串會被當 0 寫入並存進配方檔，請勿送非數值。(4) 未登錄的 ECID：S2F30 回 L,6 但名稱 / 三個界限 / 單位皆為零長度；S2F14 回一個零長度項目；S2F15 回 EAC=1。</t>
+          <t>⚠ 讀取與寫入的五個實務要點(實測範圍見各點括號)：
+(1)〔2026-08-04 實測〕S2F13 / S2F29 送 &lt;L[0]&gt; 全查時，回覆順序是本機的「註冊順序」1501、1007、2760、2758、2761、2759、2762、2763 —— 不是號碼遞增，且 Start 與 Pitch 是交錯的；S2F14 依 SEMI E5 不回 ECID(酬載為 L,n{ECV})，請以請求順序對位取值。
+(2)〔EAC=0 / 1 / 3 為 2026-08-04 實測(以 ECID 1007、1006、16000 驗證)；EAC=2 為程式碼查證、本次未實測 —— 兩段實測皆在機台閒置下進行〕EAC：0=全部受理 / 1=格式錯誤或含不可寫號碼(含唯讀的 1501 與所有未登錄號碼) / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。⚠ 忙碌閘排在號碼判定之前，因此機台忙碌時所有非 1007 的號碼一律先回 2，看不到 1。⚠ 非零的 EAC 不代表整包都沒生效 —— 本機逐筆套用：封包內若混入不可寫或未登錄的號碼，可寫的那幾筆仍會實際寫入並存檔，但整包回非零 EAC 且不發 CEID 48，即「部分成功卻回報失敗」。⚠ 反過來也成立：EAC=0 並不保證值已正確寫入 —— 若 ECV 用了本機不解析的 item 型別(F4 / F8 等)，會回 EAC=0 但實際寫入 0，見第 (5) 點。詳見「2026-08-04 第 5 版修訂」第 22 項；本方待修，修好前請依該項的兩條送包規則(1007 單獨成包；tray 幾何另成一包且只在閒置時送)。
+(3)〔ECMIN / ECMAX 為 2026-08-04 實測；tray 幾何的寫入行為為程式碼查證、本次未做 round-trip 實測〕S2F30 回報的 ECMIN / ECMAX 為零長度(未宣告，與 HT-90XX 相同)，寫入路徑也不做範圍檢查；tray 幾何若收到無法轉為數值的 ECV 會被當 0 寫入、存進當前配方的 setup.ini，且仍回 EAC=0 並發 CEID 48(看起來完全成功)，請務必只送可轉換的數值。
+(4)〔2026-08-04 實測〕未登錄的 ECID：S2F30 回 L,6 但名稱 / 三個界限 / 單位皆為零長度；S2F14 回一個零長度項目；S2F15 一律不寫入，機台閒置時回 EAC=1、運轉中或機內尚有 IC 時回 EAC=2。
+(5) ⚠〔程式碼查證，本次未實測〕S2F15 的 ECV 請一律以 ASCII 送出。本表「型別」欄是本機宣告的儲存／回報型別 —— S2F14 的回值與 S2F30 的 ECMIN / ECMAX / ECDEF 都以該型別編碼(2026-08-04 實測：ECID 2760 的 ECDEF 回 &lt;F8 0&gt;)，但它不是 S2F15 寫入時要用的 item 型別。本機的 ECV 解析只認 ASCII 與 U1 / U2 / U4 / I1 / I2 / I4；BINARY、BOOLEAN、U8、I8、F4、F8 一律不解析。⚠ 後果不是被拒絕，而是「假成功」：以 &lt;F8 102.5&gt; 寫 2760，本機取到空字串、實際寫入 0、並把 0 存進當前配方的 setup.ini，S2F16 仍回 EAC=0 並照樣發 CEID 48 —— tray 起始位置／格距被歸零，而 host 端看到的是完全成功；若同一封包還有其他 pair，該 F8 item 未被消耗會使後續解析失敗，其餘 pair 全部丟棄並回 EAC=1。正確寫法：2758-2761(F8，mm)與 2762 / 2763(I4)都以 ASCII 送，例 &lt;L,2 &lt;U4 2760&gt; &lt;A '102.5'&gt;&gt;；純整數的 2762 / 2763 亦可用 I1 / I2 / I4 / U1 / U2 / U4。⚠ 此點與 HT-9046 不同：9046 的 S2F15 有 F4 / F8 的解析分支，貴端若沿用 9046 的寫入程式碼打到本機就會踩到本項。本方認定為缺陷，將於下一批次改為「ECV 依該 EC 宣告的型別解析；不認得的型別回 EAC=1 並記錄，絕不以 0 代替」。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="69" t="inlineStr">
         <is>
-          <t>貴端 host 曾以 S2F15 寫入、但本機未登錄的 ECID (依 2026-06-08 現場 log；本機一律回 EAC=1)　—　貴端當天共 24 筆 S2F15，寫入的號碼為 1006x3、1007x4、16000x18、16002x18、16023x18、16026x18、35011x2、37007x1；其中本機有登錄的只有 1007。⚠ 也就是說同樣的 host 設定打到本機，24 筆會全部回非零 EAC，請預先知悉以免誤判為通訊故障。</t>
+          <t>貴端 host 曾以 S2F15 寫入、但本機未登錄的 ECID (依 2026-06-08 現場 log；機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2 忙碌 —— 忙碌閘排在號碼判定之前，故忙碌時的 EAC=2 並不代表該號碼可寫，閒下來再送只會改回 EAC=1，永遠不會成功)　—　貴端當天共 24 筆 S2F15，寫入的號碼為 1006x3、1007x4、16000x18、16002x18、16023x18、16026x18、35011x2、37007x1；其中本機有登錄的只有 1007。⚠ 也就是說同樣的 host 設定打到本機，24 筆會全部回非零 EAC，請預先知悉以免誤判為通訊故障。</t>
         </is>
       </c>
     </row>
@@ -11438,13 +11450,16 @@
     <col width="86" customWidth="1" style="8" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" s="8">
       <c r="A1" s="61" t="inlineStr">
         <is>
           <t>本機警報目錄(S5F5 → S5F6 全查回覆)—— 2026-08-04 實測共 481 筆，順序與回覆完全相同；S5F7 → S5F8「已啟用清單」亦為同一份 481 筆(本機無 per-ALID 啟用表，所有警報恆為啟用)。
 ALID = 警報碼字串的 31 進位多項式雜湊(alid = alid*31 + 每個字元，unsigned 32-bit)，以 UINT_4 送出；S5F1 事件與本目錄共用同一個雜湊，故同一支警報兩處的 ALID 恆等。⚠ 其中 14 筆超過 2^31-1(JAM 家族，最大 3184282107)，host 端請以無號 32 位元解析。
-⚠ ALCD 欄是本機自有的警報分類，不是 SEMI E5 的標準類別，且不能由警報碼前綴推導(例如 WAR0962 的 ALCD 是 1)。S5F1 上報時 ALCD 的 bit7 = 1(0x80|類別)表示警報發生、bit7 = 0 表示解除；本目錄的 ALCD 一律為 bit7=0 的類別值。
-⚠ 少數尚未登錄成警報碼的自由字串警報(例如安全門 / 緊急停止 / 馬達超程)其 ALID 為該字串本身的雜湊，不在本目錄內；本方已列入後續收斂項目。</t>
+⚠ ALCD 欄是本機自有的警報分類，不是 SEMI E5 的標準類別，且不能由警報碼前綴推導(例如 WAR0962 的 ALCD 是 1 而非 8)，請以本表的 ALCD 欄為準。⚠ ALCD 在兩條路徑上的意義不同：S5F6/S5F8 目錄(即本表)的 ALCD 就是類別值本身、bit7 恆為 0(2026-08-04 實測 481 筆皆為 0/1/4/5/6/8)；S5F1 事件的 ALCD 不帶類別 —— 警報發生固定送 0x80、解除固定送 0x00，低 7 位恆為 0。⚠ 請勿由 S5F1 的 ALCD 取類別(取出來恆為 0，會有 467 筆被誤判為類別 0 Jam)；要分類請以 ALID 對本表查詢，ALID 在 S5F1 與本目錄恆等。⚠ 與 HT-9046LS 的差異請留意：9046 的 S5F1 送的是「類別 + 0x80」，本機不帶類別，host 端請勿沿用「減 0x80 取類別」的解析。
+⚠ 本目錄涵蓋本機所有「已登錄的警報碼」(4xxxx 汽缸 / 5xxxx 馬達 / 6xxxx 真空 / JAM / MES / WAR)。但下列兩類警報會上報 S5F1、其 ALID 不在本目錄內 —— host 端請預留「未知 ALID」的處理路徑，勿把未知 ALID 視為通訊錯誤；這兩類的 S5F1 ALTX 一律仍帶可讀的「碼(或字串) + 訊息」，可直接顯示給操作員。
+(1) 吸嘴碼族 SUC&lt;3 位吸嘴索引&gt;&lt;1 位錯誤類型&gt;，共 12 個：索引 000/001/002/003 對應分選臂的 4 支吸嘴，錯誤類型 1=取料真空失敗、2=放料/殘料未脫離、3=途中掉料。例：SUC0001(ALID 3145192866)、SUC0011(ALID 3145192897)，其餘可依本表所述的 31 進位雜湊自行推算。⚠ 本目錄的真空類 60000-60005 是登錄值，實機不會以這 6 個代碼上報，請勿據以建表。⚠ 這是分選臂現場較常見的一族警報，請務必納入貴端建表。
+(2) 尚未登錄成警報碼的自由字串警報 —— 本機以「該訊息字串本身」當警報碼，ALID 即該字串的雜湊，故不在目錄內、也會隨字串修訂而改變。目前包括：• 安全互鎖與廠務類：Safety Door Open、Emergency Stop、Motor Power Off、Ion Fan Alarm、Air Pressure Low。• 各軸馬達「超程(soft-limit)」：以「&lt;軸別名&gt;_MotOverLimitErr」這個名稱字串上報(例如 MTrayArmX_MotOverLimitErr，ALID 2905541040)，⚠ 不是以本目錄的 5xxx8 碼上報，兩者 ALID 不同，請勿以 5xxx8 對應超程事件；唯一例外是分選臂 X 軸，它上報已登錄的 WAR0154(在目錄內)。註：馬達的其他 8 種故障(伺服警報等)仍以本目錄的數字代碼上報，不受此例外影響。• 分選臂 / TrayArm 的英文長句警報(吸嘴離開 Home 感測器、SuckZ 下降逾時、TrayArm Z 升位脫離等)。• ⚠ 語言相依：「Loader Tray has IC, please remove」是以介面語言的翻譯結果當警報碼，同一支警報在英文與中文介面的 ALID 不同，請勿假設此 ALID 固定。
+上述兩類的代碼一致性(改為上報已登錄的數字代碼)本方已列入後續收斂項目，屆時另行通知。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -257,7 +257,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -444,6 +444,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -902,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="8" min="1" max="1"/>
@@ -2030,14 +2039,14 @@
       </c>
     </row>
     <row r="106" s="8">
-      <c r="A106" s="59" t="inlineStr">
+      <c r="A106" s="70" t="inlineStr">
         <is>
           <t>2026-08-04 第 5 版修訂 Revision 5</t>
         </is>
       </c>
     </row>
     <row r="107" s="8">
-      <c r="A107" s="60" t="inlineStr">
+      <c r="A107" s="71" t="inlineStr">
         <is>
           <t>依據韌體 Firmware</t>
         </is>
@@ -2050,7 +2059,7 @@
       </c>
     </row>
     <row r="108" s="8">
-      <c r="A108" s="60" t="inlineStr">
+      <c r="A108" s="71" t="inlineStr">
         <is>
           <t>19. 新增「ECID」工作表(第 5 張)</t>
         </is>
@@ -2062,7 +2071,7 @@
       </c>
     </row>
     <row r="109" s="8">
-      <c r="A109" s="60" t="inlineStr">
+      <c r="A109" s="71" t="inlineStr">
         <is>
           <t>20. 新增「ALID」工作表(第 6 張)</t>
         </is>
@@ -2074,7 +2083,7 @@
       </c>
     </row>
     <row r="110" s="8">
-      <c r="A110" s="60" t="inlineStr">
+      <c r="A110" s="71" t="inlineStr">
         <is>
           <t>21. 更正「功能」表的 EC 筆數與可寫規則</t>
         </is>
@@ -2088,7 +2097,7 @@
     <row r="111" s="8">
       <c r="A111" s="61" t="inlineStr">
         <is>
-          <t>⚠ 22. 新發現缺陷：S2F15 的兩個寫入缺陷(本方待修)</t>
+          <t>⚠ 22. 新發現缺陷：S2F15 的兩個寫入缺陷(本方待修)〔20260804 追加項：兩者皆已修復並實測〕</t>
         </is>
       </c>
       <c r="B111" s="61" t="inlineStr">
@@ -2097,24 +2106,26 @@
 依程式碼判讀，同一現象在機台忙碌時亦成立：此時 1006 讓整包 EAC 變成 2，但 1007 的處理排在忙碌閘之前，仍然寫入(⚠ 此點尚未實測，本版實測皆在機台閒置下進行 —— 見本表「驗證」第 3 點)。另外，貴端當天 17:51:58 還有一筆是 L[2]{L[2]{1007,"AGV"},L[2]{37007,1}}，37007 本機亦未登錄，故該形狀也會踩到同一個現象 —— 問題不限於 1006。
 本方認定為缺陷，將於下一批次修正為「先整包檢查、全部可寫才逐筆套用」(對齊 HT9045)。⚠ 在修正版交機之前，請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一包，不得混入本機不可寫或未登錄的號碼，並僅在機台閒置且機內無 IC 時送出。⚠ 「整包都是可寫的號碼」並不等於安全：運轉中送 {1007＋任一 tray 幾何} 時 1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進配方檔 —— 被靜默改動的是會影響取放座標的機構參數。成因是持久化與事件的判斷條件不同：寫入與存檔只看「該筆是否寫成功」，而 CEID 48 只在整包 EAC=0 時才發。
 附帶提醒：貴端當天 24 筆 S2F15 所寫的號碼中，本機只登錄 1007 一個，因此同一份 host 設定打到本機時 24 筆都會回非零 EAC(其中 4 筆含 1007 者會實際寫入)。
-⚠ 缺陷二(2026-08-04 同時發現，程式碼查證)：S2F15 的 ECV 型別解析不完整。本機的 ECV 只認 ASCII 與 U1/U2/U4/I1/I2/I4；F4 / F8 / BOOLEAN / BINARY / U8 / I8 一律不解析，而且不是回錯誤 —— 取到空字串後當 0 寫入、存進當前配方的 setup.ini，並仍回 EAC=0 且照發 CEID 48。也就是 host 以合乎規格的 &lt;F8 102.5&gt; 寫 ECID 2760，會得到「完全成功」的回覆而 tray 起始位置被歸零。⚠ HT-9046 的 S2F15 有 F4/F8 的解析分支，貴端若沿用 9046 的寫入程式碼打到本機就會踩到。過渡辦法：ECV 一律以 ASCII 送(例 &lt;L,2 &lt;U4 2760&gt; &lt;A '102.5'&gt;&gt;)。本方將於下一批次改為「依該 EC 宣告的型別解析；不認得的型別回 EAC=1 並記錄，絕不以 0 代替」。</t>
+⚠ 缺陷二(2026-08-04 同時發現，程式碼查證)：S2F15 的 ECV 型別解析不完整。本機的 ECV 只認 ASCII 與 U1/U2/U4/I1/I2/I4；F4 / F8 / BOOLEAN / BINARY / U8 / I8 一律不解析，而且不是回錯誤 —— 取到空字串後當 0 寫入、存進當前配方的 setup.ini，並仍回 EAC=0 且照發 CEID 48。也就是 host 以合乎規格的 &lt;F8 102.5&gt; 寫 ECID 2760，會得到「完全成功」的回覆而 tray 起始位置被歸零。⚠ HT-9046 的 S2F15 有 F4/F8 的解析分支，貴端若沿用 9046 的寫入程式碼打到本機就會踩到。過渡辦法：ECV 一律以 ASCII 送(例 &lt;L,2 &lt;U4 2760&gt; &lt;A '102.5'&gt;&gt;)。本方將於下一批次改為「依該 EC 宣告的型別解析；不認得的型別回 EAC=1 並記錄，絕不以 0 代替」。
+〔20260804 追加項：以上兩個缺陷都已修復並以實機 round-trip 驗證，詳見本表末「2026-08-04 第 5 版 追加項」第 26、27 項。修正後：混合封包整包拒絕(實測 {1006,1007} → EAC=1、Operator ID 維持原值、無 CEID 48)、F8 / F4 / BOOLEAN 的 ECV 已可解析(實測 &lt;F8 71.5&gt; → EAC=0、值為 71.5)、無法轉為數值的值一律 EAC=3 不寫入(實測 'abc' → EAC=3、值不變)。⚠ 本項所述的舊行為僅適用於 2026-08-04 之前的韌體；貴端機台若尚未更新，請仍照本項的送包規則。〕</t>
         </is>
       </c>
     </row>
     <row r="112" s="8">
-      <c r="A112" s="60" t="inlineStr">
-        <is>
-          <t>⚠ 23. EC 側名稱與 HT-90XX / 本機 SV 側不一致(本方擬對齊)</t>
+      <c r="A112" s="61" t="inlineStr">
+        <is>
+          <t>⚠ 23. EC 側名稱與 HT-90XX / 本機 SV 側不一致(本方擬對齊)〔20260804 追加項：已執行〕</t>
         </is>
       </c>
       <c r="B112" s="61" t="inlineStr">
         <is>
-          <t>本機同一個號碼在 EC 與 SV 兩個命名空間登錄了不同的名稱字串：1501 EC 回「Recipe Name」而 SV 回「Setup File」(HT-90XX 為 Setup File)；2758-2763 EC 回「Tray X Pitch」等短名，而 SV 回「Type 1 Tray Pitch X」等(HT-90XX 為後者)。號碼、型別、單位與數值三方完全一致，只有 S2F30 / S1F12 回覆的名稱字串不同。依貴端「相同功能使用同一編號」的原則，本方擬在下一批次把 EC 側名稱一併對齊 HT-90XX(僅改字串，不動號碼與行為)。⚠ 請貴端以號碼綁定，不要以名稱字串比對。</t>
+          <t>本機同一個號碼在 EC 與 SV 兩個命名空間登錄了不同的名稱字串：1501 EC 回「Recipe Name」而 SV 回「Setup File」(HT-90XX 為 Setup File)；2758-2763 EC 回「Tray X Pitch」等短名，而 SV 回「Type 1 Tray Pitch X」等(HT-90XX 為後者)。號碼、型別、單位與數值三方完全一致，只有 S2F30 / S1F12 回覆的名稱字串不同。依貴端「相同功能使用同一編號」的原則，本方擬在下一批次把 EC 側名稱一併對齊 HT-90XX(僅改字串，不動號碼與行為)。⚠ 請貴端以號碼綁定，不要以名稱字串比對。
+〔20260804 追加項：已執行 —— EC 側名稱已改為 Setup File 與 Type 1 Tray … 全名，與本機 SV 側及貴端機台逐字相同。實測 S2F29 &lt;L[0]&gt; 的 8 個名稱與 HT-90XX 宣告字串完全一致。號碼、型別、單位、值與所有訊息形狀皆未變 —— 只有 S2F30 / S1F12 回覆的名稱字串改變。⚠ 以名稱字串比對 EC 的 host 請以本版為準；以號碼綁定者不受影響。〕</t>
         </is>
       </c>
     </row>
     <row r="113" s="8">
-      <c r="A113" s="60" t="inlineStr">
+      <c r="A113" s="71" t="inlineStr">
         <is>
           <t>24. 更正檔首與各版註記的過時數字</t>
         </is>
@@ -2126,7 +2137,7 @@
       </c>
     </row>
     <row r="114" s="8">
-      <c r="A114" s="60" t="inlineStr">
+      <c r="A114" s="71" t="inlineStr">
         <is>
           <t>25. 更正 Open item 6(Off-Line 仍能下命令)的現況敘述</t>
         </is>
@@ -2138,14 +2149,14 @@
       </c>
     </row>
     <row r="115" s="8">
-      <c r="A115" s="59" t="inlineStr">
+      <c r="A115" s="70" t="inlineStr">
         <is>
           <t>尚待貴端裁定 / 確認 Open items (2026-08-04 新增)</t>
         </is>
       </c>
     </row>
     <row r="116" s="8">
-      <c r="A116" s="60" t="inlineStr">
+      <c r="A116" s="71" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2163,7 +2174,7 @@
       </c>
     </row>
     <row r="117" s="8">
-      <c r="A117" s="60" t="inlineStr">
+      <c r="A117" s="71" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2177,7 +2188,7 @@
       </c>
     </row>
     <row r="118" s="8">
-      <c r="A118" s="60" t="inlineStr">
+      <c r="A118" s="71" t="inlineStr">
         <is>
           <t>本次未變動 Unchanged</t>
         </is>
@@ -2189,7 +2200,7 @@
       </c>
     </row>
     <row r="119" s="8">
-      <c r="A119" s="60" t="inlineStr">
+      <c r="A119" s="71" t="inlineStr">
         <is>
           <t>第 5 版的驗證 Verification</t>
         </is>
@@ -2210,6 +2221,95 @@
 • EAC=2(機台忙碌)本次亦未實測 —— 兩段實測皆在機台閒置下進行(ECID 1006 回 EAC=1 即為閒置之證；忙碌時同一筆會回 EAC=2)。
 • tray 幾何 2758-2763 的 S2F15 寫入本次完全未實測 —— 兩段 round-trip 只對 ECID 1007、1006、16000 送過 S2F15，2758-2763 僅有讀取(S2F13/S2F14、S1F3/S1F4、S2F29/S2F30)。故下列三項目前僅為程式碼查證：idle 閘的實際擋阻、無法解出數值的 ECV 會被當 0 寫入並存進配方檔(且仍回 EAC=0 並發 CEID 48)、以及本機實際可接受的 ECV 型別範圍(第 22 項第二個缺陷)。本方將於下一批次補測並回報。
 • 第 22 項的兩個缺陷尚未修正；8bf575c 的汽缸逾時尚待上機以實際 reed 驗證；整體上機驗證待執行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" s="8">
+      <c r="A121" s="70" t="inlineStr">
+        <is>
+          <t>2026-08-04 第 5 版 追加項(同日，承第 5 版)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" s="8">
+      <c r="A122" s="71" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B122" s="61" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (S2F15 兩項寫入缺陷修正 + EC 名稱對齊 HT-90XX)。本追加項是本日第 5 版第 22、23 兩項的實作結果 —— 該兩項在第 5 版發出時列為「本方待修 / 擬對齊」，現已完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" s="8">
+      <c r="A123" s="71" t="inlineStr">
+        <is>
+          <t>⚠ 26. S2F15 改為「全有全無」(第 22 項缺陷一，已修)</t>
+        </is>
+      </c>
+      <c r="B123" s="61" t="inlineStr">
+        <is>
+          <t>S2F15 的處理改為兩段式，與 HT9045 的 check / update 兩段一致：先解析並檢查封包內的每一筆，任一筆不通過就整包拒絕、完全不寫入、也不發 CEID 48；只有整包通過才逐筆寫入並發一次 CEID 48。修正前是逐筆立即套用而 EAC 只有一個值，導致混合封包「已寫入卻回報失敗且不通知」。
+• 多筆同時失敗時的 EAC 優先序為 1 &gt; 3 &gt; 2，因為 1 代表「這個號碼永遠不會被接受」、2 代表「等閒置重送即可」，把最可行動的資訊回給 host。
+• 單筆 1007 的行為完全不變(不受 idle 閘、成功回 EAC=0 並發 CEID 48、空字串回 EAC=3)。
+• 實測：{1006,1007} → EAC=1，Operator ID 維持原值、無 CEID 48(修正前為值已寫入卻回 EAC=1)；{1007 空字串, 2760 有效值} → EAC=3，tray 值不變(修正前 tray 值會被寫入並存進配方檔)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" s="8">
+      <c r="A124" s="71" t="inlineStr">
+        <is>
+          <t>⚠ 27. S2F15 的 ECV 型別解析補齊 + 非數值一律拒絕(第 22 項缺陷二，已修)</t>
+        </is>
+      </c>
+      <c r="B124" s="61" t="inlineStr">
+        <is>
+          <t>本機的 ECV 解析原本只認 ASCII 與 U1-U4 / I1-I4，F8 / F4 / BOOLEAN 落到「不認得」分支且呼叫端未檢查回傳值，結果是取到空字串、當 0 寫入、卻仍回 EAC=0 並發 CEID 48 —— host 送一筆合法的 &lt;F8 102.5&gt; 設 tray 格距，會把幾何歸零而看到「完全成功」。本追加項：
+• 補上 F8 / F4 / BOOLEAN 的解析，貴端可直接用本檔「ECID」工作表「型別」欄的型別送，也可一律用 ASCII，兩者等效(這也讓沿用 HT-9046 寫入程式碼的 host 直接可用 —— 9046 本來就支援 F4/F8)。
+• 讀不出來的型別(BINARY、U8、I8)一律回 EAC=1 並整包不寫入，絕不以 0 代替。
+• tray 幾何另加「可否轉為數值」檢查：2758-2761 需可轉浮點、2762/2763 需可轉整數，否則回 EAC=3 並整包不寫入(修正前 ASCII 'abc' 會被當 0 寫入並存進配方檔且回 EAC=0)。註：本機仍不做「範圍」檢查(ECMIN / ECMAX 未宣告，與 HT-90XX 相同)，超出機構行程的合法數值仍會被接受。
+• 實測：&lt;F8 71.5&gt; 寫 2760 → EAC=0 且值為 71.5；ASCII '70.25' → EAC=0 且值為 70.25；ASCII 'abc' → EAC=3 且值不變；未登錄的 16000 → EAC=1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" s="8">
+      <c r="A125" s="71" t="inlineStr">
+        <is>
+          <t>28. EC 名稱對齊 HT-90XX(第 23 項，已執行)</t>
+        </is>
+      </c>
+      <c r="B125" s="61" t="inlineStr">
+        <is>
+          <t>EC 側的名稱字串改為與本機 SV 側及 HT-90XX 逐字相同：1501 由「Recipe Name」改為「Setup File」；2758 / 2759 改為「Type 1 Tray Pitch X / Y」；2760 / 2761 改為「Type 1 Tray Start Position X / Y」；2762 / 2763 改為「Type 1 Tray Division X / Y」。1007 Operator ID 原本即與 9045 相同、未變。
+⚠ 只有 S2F30 / S1F12 回覆的名稱字串改變 —— 號碼、型別、單位、值、以及所有訊息的形狀與時序完全不變。以號碼綁定的 host 不受影響；若貴端有以名稱字串比對 EC 的程式，請以本版為準。本檔「ECID」工作表的名稱欄已同步更新為實測回覆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" s="8">
+      <c r="A126" s="71" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B126" s="61" t="inlineStr">
+        <is>
+          <t>CEID 的編號、語意與發射點、SVID 的編號與名稱、預設 Report 1 的 13 個 SV 內容與順序、S1F23/S1F24 與 S2F29/S2F30 的回覆形狀與筆數(仍為 8 個 EC)、S5 警報目錄的內容與筆數(481)、Soter 輸出檔契約 —— 全部未變。EC 的可寫範圍亦未變(仍為 1007 與 2758-2763)：本追加項只改變「不合格的封包如何被拒絕」與「ECV 可用哪些型別表達」，不放寬也不收緊任何號碼的可寫性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" s="8">
+      <c r="A127" s="71" t="inlineStr">
+        <is>
+          <t>追加項的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B127" s="61" t="inlineStr">
+        <is>
+          <t>1. 建置：模擬版 -Clean exit 0；註銷 SOFT_SIMULATE 之真機版 -Full exit 0；還原後再 -Full exit 0；原始碼編碼檢查 166 檔通過。
+2. 以 headless SECS host 對重新建置的實際韌體做 HSMS round-trip 迴歸實測，9 項全部通過：(A) S2F29 &lt;L[0]&gt; 的 8 個 EC 名稱與 HT-90XX 宣告字串逐字相同；(B) 單筆 1007 → EAC=0、值寫入、收到 CEID 48；(C) 混合封包 {1006,1007} → EAC=1、1007 維持原值、無 CEID 48；(D) {1007 空字串, 2760 有效值} → EAC=3、tray 值不變；(E) ASCII 寫 2760=70.25 → EAC=0、值為 70.25、收到 CEID 48；(F) &lt;F8 71.5&gt; 寫 2760 → EAC=0、值為 71.5(修正前為 0)；(G) ASCII 'abc' 寫 2760 → EAC=3、值不變(修正前寫入 0 並回 EAC=0)；(H) 未登錄的 16000 → EAC=1；(I) 所有被改動的值最後皆還原並複讀確認(1007 / 2758 / 2760 / 2762 全部回到原值)。
+3. ⚠ 尚未驗證：機台「運轉中」的路徑仍未實測(EAC=2 與 1007 運轉中寫入)；上機驗證待執行。</t>
         </is>
       </c>
     </row>
@@ -2521,8 +2621,8 @@
   &gt;
 .
 [20260804] 已實作。可寫的 EC 只有兩組：ECID 1007 Operator ID(不受 idle 閘，運轉中亦可寫)與 2758-2763 Tray 幾何(僅機台閒置且機內無 IC 時受理)。其餘號碼(含已登錄但唯讀的 1501)一律不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)。⚠ 忙碌閘排在號碼判定之前，故 EAC=2 只代表當下忙碌、不代表該號碼可寫 —— 對本機不可寫或未登錄的號碼，閒下來再送只會由 2 改成 1，永遠不會成功。EAC：0=全部受理 / 1=封包格式錯誤或含不可寫的號碼 / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。
-⚠ 混合封包請拆開送(2026-08-04 實測)。S2F16 的 EAC 是「整包一個值」，而本機是逐筆套用。以貴端 2026-06-08 對 HT-9046 送的同一種封包 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 實測本機：1007 的值確實已寫入並存檔(可由 S2F13 讀回)，但整包回 EAC=1、且不發 CEID 48 —— 「部分成功卻回報失敗」。HT-9046 不會如此(它的忙碌閘是整包擋在寫入之前)。依程式碼判讀，同一現象在機台忙碌時亦會發生(此時整包回 EAC=2，1007 仍已寫入 —— 因為 1007 的處理排在忙碌閘之前)；⚠ 此忙碌情形尚未實測，2026-08-04 的實測全部在機台閒置下進行(實得 EAC 僅 0 / 1 / 3)，本方將於上機驗證時補齊。貴端當天另有一筆是把 1007 與 37007 包在一起，37007 本機同樣未登錄，故該形狀也會踩到同一個現象。本方已列為缺陷待修(見「2026-08-04 第 5 版修訂」第 22 項)；在修好之前，⚠ 請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成為一個封包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一個封包，不得混入本機不可寫或未登錄的號碼(1501、1006、37007、16000、16002、16023、16026、35011 等)，並僅在機台閒置且機內無 IC 時送出。⚠ 特別提醒：「整包都是可寫的號碼」並不等於安全 —— 因為 1007 排在忙碌閘之前，運轉中送 {1007＋任一 tray 幾何} 時，1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2 且不發事件；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進當前配方檔(存檔只看該筆是否寫成功，不看 EAC)。原則：一個封包只放一個號碼最安全，最低限度是 1007 絕不與其他號碼同包。不含 1007 的純 tray 幾何封包是全有全無(忙碌時整包拒絕、閒置時整包寫入並發 CEID 48)，可安全合併。
-⚠ 另請注意：S2F30 回報的 ECMIN / ECMAX 目前是零長度(未宣告，與 HT9045 相同)，寫入路徑也不做數值範圍檢查；tray 幾何若無法解出數值就會被當 0 寫入並存進配方檔。⚠ 這不只發生在非數值字串 —— 以 F4 / F8 item 送出的「合法數值」在本機同樣解不出來，會被當 0 寫入卻仍回 EAC=0 並發 CEID 48(HT-9046 的 S2F15 有 F4/F8 分支，本機沒有，貴端若沿用 9046 的寫入程式碼會踩到)。請一律以 ASCII 送 ECV，並勿送非數值。詳見「ECID」工作表第 (5) 點。</t>
+⚠ 混合封包請拆開送(2026-08-04 實測)。S2F16 的 EAC 是「整包一個值」，而本機是逐筆套用。以貴端 2026-06-08 對 HT-9046 送的同一種封包 L[2]{L[2]{1006,批號},L[2]{1007,操作員}} 實測本機：1007 的值確實已寫入並存檔(可由 S2F13 讀回)，但整包回 EAC=1、且不發 CEID 48 —— 「部分成功卻回報失敗」。HT-9046 不會如此(它的忙碌閘是整包擋在寫入之前)。依程式碼判讀，同一現象在機台忙碌時亦會發生(此時整包回 EAC=2，1007 仍已寫入 —— 因為 1007 的處理排在忙碌閘之前)；⚠ 此忙碌情形尚未實測，2026-08-04 的實測全部在機台閒置下進行(實得 EAC 僅 0 / 1 / 3)，本方將於上機驗證時補齊。貴端當天另有一筆是把 1007 與 37007 包在一起，37007 本機同樣未登錄，故該形狀也會踩到同一個現象。〔20260804 追加項：本缺陷已修復並實測通過 —— S2F15 改為「先整包檢查、全部可寫且不忙碌才逐筆套用」，混合封包現在一律整包拒絕、完全不寫入、也不發 CEID 48(實測 {1006,1007} 回 EAC=1 且 Operator ID 維持原值)。同時 ECV 的型別解析已補齊(F8 / F4 / BOOLEAN 現在都讀得出來)，且無法轉為數值的 tray 值一律回 EAC=3 不寫入，不再出現「靜默寫 0」。因此下列兩條送包規則對修正後的韌體已非必要；若貴端機台尚未更新韌體，請仍照下列規則送〕在舊版韌體上，⚠ 請依兩條規則送 S2F15：(1) ECID 1007 一律單獨成為一個封包，不與任何其他號碼同包；(2) tray 幾何 2758-2763 另成一個封包，不得混入本機不可寫或未登錄的號碼(1501、1006、37007、16000、16002、16023、16026、35011 等)，並僅在機台閒置且機內無 IC 時送出。⚠ 特別提醒：「整包都是可寫的號碼」並不等於安全 —— 因為 1007 排在忙碌閘之前，運轉中送 {1007＋任一 tray 幾何} 時，1007 會寫入而 tray 幾何被忙碌閘擋下，整包回 EAC=2 且不發事件；閒置時送 {1007 空字串＋有效 tray 幾何} 則整包回 EAC=3，但 tray 幾何已寫入並存進當前配方檔(存檔只看該筆是否寫成功，不看 EAC)。原則：一個封包只放一個號碼最安全，最低限度是 1007 絕不與其他號碼同包。不含 1007 的純 tray 幾何封包是全有全無(忙碌時整包拒絕、閒置時整包寫入並發 CEID 48)，可安全合併。
+⚠ 另請注意：S2F30 回報的 ECMIN / ECMAX 目前是零長度(未宣告，與 HT9045 相同)，寫入路徑也不做數值範圍檢查；tray 幾何若無法解出數值就會被當 0 寫入並存進配方檔。〔20260804 追加項：已修 —— 現在 ASCII 與 F8 / F4 / BOOLEAN、U1-U4 / I1-I4 都可作為 ECV 送出，本機依收到的型別解出數值；無法轉為數值者(例如 ASCII 'abc'、空 item)一律回 EAC=3 且不寫入，不會再出現「回 EAC=0 卻寫進 0」。舊版韌體則會 —— 若貴端機台尚未更新，請一律以 ASCII 送 ECV。實測：&lt;F8 71.5&gt; 寫 2760 得 EAC=0 且值為 71.5；ASCII 'abc' 得 EAC=3 且值不變。詳見「ECID」工作表第 (5) 點。〕</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2651,7 @@
   &lt;L [0] 
   &gt;
 .
-[20260730] 已實作(2026-07-30 新增)。S2F29 -&gt; S2F30 回 L,n{L,6{U4 ECID, A ECNAME, ECMIN, ECMAX, ECDEF, A ECUNITS}}。&lt;L[0]&gt; 全查回全部 8 個 EC，回覆順序即本機的註冊順序(不是號碼遞增)：1501 Recipe Name、1007 Operator ID、2760 Tray X Start、2758 Tray X Pitch、2761 Tray Y Start、2759 Tray Y Pitch、2762 Tray X Division、2763 Tray Y Division。〔20260804 更正：原文「7 個」是 2026-08-03 新增 ECID 1007 之前的數字；全查的 L 長度已由 7 變 8，請以回覆內的 ECID 對號取值，勿以固定筆數或固定位置解析。〕ECMIN / ECMAX / ECDEF 以該 EC 自身宣告的型別編碼(例如 FT_8 的 Tray X Start 回 FT_8，不是 ASCII)；未宣告上下限者回該型別的零長度項目(E5「未宣告」的表示法，與 HT9045 相同)。未註冊的 ECID 回 L,6 內名稱 / 三個界限 / 單位皆為零長度。註：本訊息為唯讀查詢；EC 寫入仍走 S2F15，維持「只開放 tray 幾何(2758-2763)」與「機台閒置才受理」兩道限制，S2F30 不會放寬可寫範圍。〔20260804 更正：自 2026-08-03 起唯一的例外是 ECID 1007 Operator ID —— 它不是 tray 幾何，且刻意不受 idle 閘、運轉中亦接受寫入(空字串回 EAC=3)。貴端 2026-06-08 現場在運轉當下寫 ECID 1007 = "AGV" 的那幾筆，在本機會被受理，不會被拒。〕
+[20260730] 已實作(2026-07-30 新增)。S2F29 -&gt; S2F30 回 L,n{L,6{U4 ECID, A ECNAME, ECMIN, ECMAX, ECDEF, A ECUNITS}}。&lt;L[0]&gt; 全查回全部 8 個 EC，回覆順序即本機的註冊順序(不是號碼遞增)：1501 Setup File、1007 Operator ID、2760 Type 1 Tray Start Position X、2758 Type 1 Tray Pitch X、2761 Type 1 Tray Start Position Y、2759 Type 1 Tray Pitch Y、2762 Type 1 Tray Division X、2763 Type 1 Tray Division Y〔20260804 追加項：名稱已對齊 HT-90XX，1501 由 Recipe Name 改為 Setup File、2758-2763 由短名改為 Type 1 … 全名，與本機 SV 側及貴端機台完全相同；號碼、型別、單位與值皆未變〕。〔20260804 更正：原文「7 個」是 2026-08-03 新增 ECID 1007 之前的數字；全查的 L 長度已由 7 變 8，請以回覆內的 ECID 對號取值，勿以固定筆數或固定位置解析。〕ECMIN / ECMAX / ECDEF 以該 EC 自身宣告的型別編碼(例如 FT_8 的 Tray X Start 回 FT_8，不是 ASCII)；未宣告上下限者回該型別的零長度項目(E5「未宣告」的表示法，與 HT9045 相同)。未註冊的 ECID 回 L,6 內名稱 / 三個界限 / 單位皆為零長度。註：本訊息為唯讀查詢；EC 寫入仍走 S2F15，維持「只開放 tray 幾何(2758-2763)」與「機台閒置才受理」兩道限制，S2F30 不會放寬可寫範圍。〔20260804 更正：自 2026-08-03 起唯一的例外是 ECID 1007 Operator ID —— 它不是 tray 幾何，且刻意不受 idle 閘、運轉中亦接受寫入(空字串回 EAC=3)。貴端 2026-06-08 現場在運轉當下寫 ECID 1007 = "AGV" 的那幾筆，在本機會被受理，不會被拒。〕
 [20260804] 本機的 EC 目錄已列於本檔新增的「ECID」工作表(第 5 張)，含號碼 / 名稱 / 型別 / 單位 / 可寫性 / 說明，以及貴端 host 曾以 S2F15 寫入但本機未登錄的號碼清單。該表內容係以 headless SECS host 對實際韌體實測 S2F29 &lt;L[0]&gt; 的回覆逐格記錄，非人工整理。</t>
         </is>
       </c>
@@ -10893,10 +10993,10 @@
           <t>名稱 Name (S2F30 實際回覆)</t>
         </is>
       </c>
-      <c r="C2" s="63" t="inlineStr">
+      <c r="C2" s="72" t="inlineStr">
         <is>
           <t>型別
-(本機宣告；S2F14 / S2F30 以此編碼，非 S2F15 寫入用的 item 型別 —— 見第 (5) 點)</t>
+(本機宣告；S2F14 / S2F30 以此編碼。S2F15 寫入可用 ASCII 或本欄型別 —— 見第 (5) 點)</t>
         </is>
       </c>
       <c r="D2" s="63" t="inlineStr">
@@ -10921,7 +11021,7 @@
       </c>
       <c r="B3" s="65" t="inlineStr">
         <is>
-          <t>Recipe Name</t>
+          <t>Setup File</t>
         </is>
       </c>
       <c r="C3" s="64" t="inlineStr">
@@ -10941,7 +11041,7 @@
       </c>
       <c r="F3" s="65" t="inlineStr">
         <is>
-          <t>目前配方(Setup File)名。⚠ SV 側同號的名稱是 Setup File(與 HT-90XX 一致)，EC 側目前回 Recipe Name，本方擬於下一批次對齊(見第 5 版第 23 項)。S2F15 寫入不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況都不寫入，EAC=2 不表示稍後重送會成功。</t>
+          <t>目前配方(Setup File)名。名稱已於 2026-08-04 由 Recipe Name 對齊為 Setup File，與本機 SV 側及 HT-90XX 完全相同(見「追加項」第 28 項)。S2F15 寫入不受理：機台閒置時回 EAC=1，運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況都不寫入，EAC=2 不表示稍後重送會成功。</t>
         </is>
       </c>
     </row>
@@ -10971,7 +11071,7 @@
       </c>
       <c r="F4" s="65" t="inlineStr">
         <is>
-          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入(此點為程式碼判讀，運轉中的實機寫入尚未實測，見第 5 版「驗證」第 3 點)，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。單獨送 1007 一筆且寫入成功時：回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC。⚠ 若與其他不可寫的號碼包在同一封包，值仍會寫入並存檔，但整包回非零 EAC 且不發 CEID 48(見下方註記與第 5 版第 22 項)；空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
+          <t>本班作業人員身分，出廠預設 "Operator"。⚠ 這是 idle 閘的唯一例外 —— 運轉中也接受寫入(此點為程式碼判讀，運轉中的實機寫入尚未實測，見第 5 版「驗證」第 3 點)，理由是它只是識別字串、無機構後果，而貴端正是在運轉當下寫它。單獨送 1007 一筆且寫入成功時：回 EAC=0、即時顯示於主畫面、寫入 General.ini 保存、並發 CEID 48 Change EC。⚠ 若與其他不可寫的號碼包在同一封包，整包會被拒絕、1007 也不會被寫入(2026-08-04 追加項後的行為，實測 {1006,1007} → EAC=1 且本欄維持原值)；⚠ 在 2026-08-04 之前的韌體上，該封包會「已寫入卻回報失敗」(見第 5 版第 22 項)。空字串一律回 EAC=3 不予寫入(確保本欄永不回空)。同號 SVID 1007 可讀。</t>
         </is>
       </c>
     </row>
@@ -10981,7 +11081,7 @@
       </c>
       <c r="B5" s="65" t="inlineStr">
         <is>
-          <t>Tray X Start</t>
+          <t>Type 1 Tray Start Position X</t>
         </is>
       </c>
       <c r="C5" s="64" t="inlineStr">
@@ -11001,7 +11101,7 @@
       </c>
       <c r="F5" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 起始位置 X。SV 側名稱為 Type 1 Tray Start Position X。</t>
+          <t>Type 1 Tray 起始位置 X。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11111,7 @@
       </c>
       <c r="B6" s="65" t="inlineStr">
         <is>
-          <t>Tray X Pitch</t>
+          <t>Type 1 Tray Pitch X</t>
         </is>
       </c>
       <c r="C6" s="64" t="inlineStr">
@@ -11031,7 +11131,7 @@
       </c>
       <c r="F6" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 格距 X。SV 側名稱為 Type 1 Tray Pitch X。</t>
+          <t>Type 1 Tray 格距 X。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11141,7 @@
       </c>
       <c r="B7" s="65" t="inlineStr">
         <is>
-          <t>Tray Y Start</t>
+          <t>Type 1 Tray Start Position Y</t>
         </is>
       </c>
       <c r="C7" s="64" t="inlineStr">
@@ -11061,7 +11161,7 @@
       </c>
       <c r="F7" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 起始位置 Y。SV 側名稱為 Type 1 Tray Start Position Y。</t>
+          <t>Type 1 Tray 起始位置 Y。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11171,7 @@
       </c>
       <c r="B8" s="65" t="inlineStr">
         <is>
-          <t>Tray Y Pitch</t>
+          <t>Type 1 Tray Pitch Y</t>
         </is>
       </c>
       <c r="C8" s="64" t="inlineStr">
@@ -11091,7 +11191,7 @@
       </c>
       <c r="F8" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 格距 Y。SV 側名稱為 Type 1 Tray Pitch Y。</t>
+          <t>Type 1 Tray 格距 Y。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11201,7 @@
       </c>
       <c r="B9" s="65" t="inlineStr">
         <is>
-          <t>Tray X Division</t>
+          <t>Type 1 Tray Division X</t>
         </is>
       </c>
       <c r="C9" s="64" t="inlineStr">
@@ -11121,7 +11221,7 @@
       </c>
       <c r="F9" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 每列格數 X。SV 側名稱為 Type 1 Tray Division X。</t>
+          <t>Type 1 Tray 每列格數 X。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11231,7 @@
       </c>
       <c r="B10" s="65" t="inlineStr">
         <is>
-          <t>Tray Y Division</t>
+          <t>Type 1 Tray Division Y</t>
         </is>
       </c>
       <c r="C10" s="64" t="inlineStr">
@@ -11151,19 +11251,19 @@
       </c>
       <c r="F10" s="65" t="inlineStr">
         <is>
-          <t>Type 1 Tray 每欄格數 Y。SV 側名稱為 Type 1 Tray Division Y。</t>
+          <t>Type 1 Tray 每欄格數 Y。EC 與 SV 兩側的名稱自 2026-08-04 起完全相同(見「追加項」第 28 項)。</t>
         </is>
       </c>
     </row>
     <row r="12" s="8">
       <c r="A12" s="61" t="inlineStr">
         <is>
-          <t>⚠ 讀取與寫入的五個實務要點(實測範圍見各點括號)：
+          <t>⚠ 讀取與寫入的五個實務要點(實測範圍見各點括號；本表已含 2026-08-04「追加項」的 S2F15 修正)：
 (1)〔2026-08-04 實測〕S2F13 / S2F29 送 &lt;L[0]&gt; 全查時，回覆順序是本機的「註冊順序」1501、1007、2760、2758、2761、2759、2762、2763 —— 不是號碼遞增，且 Start 與 Pitch 是交錯的；S2F14 依 SEMI E5 不回 ECID(酬載為 L,n{ECV})，請以請求順序對位取值。
-(2)〔EAC=0 / 1 / 3 為 2026-08-04 實測(以 ECID 1007、1006、16000 驗證)；EAC=2 為程式碼查證、本次未實測 —— 兩段實測皆在機台閒置下進行〕EAC：0=全部受理 / 1=格式錯誤或含不可寫號碼(含唯讀的 1501 與所有未登錄號碼) / 2=機台忙碌(運轉中或機內有 IC，1007 除外) / 3=1007 送空字串。⚠ 忙碌閘排在號碼判定之前，因此機台忙碌時所有非 1007 的號碼一律先回 2，看不到 1。⚠ 非零的 EAC 不代表整包都沒生效 —— 本機逐筆套用：封包內若混入不可寫或未登錄的號碼，可寫的那幾筆仍會實際寫入並存檔，但整包回非零 EAC 且不發 CEID 48，即「部分成功卻回報失敗」。⚠ 反過來也成立：EAC=0 並不保證值已正確寫入 —— 若 ECV 用了本機不解析的 item 型別(F4 / F8 等)，會回 EAC=0 但實際寫入 0，見第 (5) 點。詳見「2026-08-04 第 5 版修訂」第 22 項；本方待修，修好前請依該項的兩條送包規則(1007 單獨成包；tray 幾何另成一包且只在閒置時送)。
-(3)〔ECMIN / ECMAX 為 2026-08-04 實測；tray 幾何的寫入行為為程式碼查證、本次未做 round-trip 實測〕S2F30 回報的 ECMIN / ECMAX 為零長度(未宣告，與 HT-90XX 相同)，寫入路徑也不做範圍檢查；tray 幾何若收到無法轉為數值的 ECV 會被當 0 寫入、存進當前配方的 setup.ini，且仍回 EAC=0 並發 CEID 48(看起來完全成功)，請務必只送可轉換的數值。
-(4)〔2026-08-04 實測〕未登錄的 ECID：S2F30 回 L,6 但名稱 / 三個界限 / 單位皆為零長度；S2F14 回一個零長度項目；S2F15 一律不寫入，機台閒置時回 EAC=1、運轉中或機內尚有 IC 時回 EAC=2。
-(5) ⚠〔程式碼查證，本次未實測〕S2F15 的 ECV 請一律以 ASCII 送出。本表「型別」欄是本機宣告的儲存／回報型別 —— S2F14 的回值與 S2F30 的 ECMIN / ECMAX / ECDEF 都以該型別編碼(2026-08-04 實測：ECID 2760 的 ECDEF 回 &lt;F8 0&gt;)，但它不是 S2F15 寫入時要用的 item 型別。本機的 ECV 解析只認 ASCII 與 U1 / U2 / U4 / I1 / I2 / I4；BINARY、BOOLEAN、U8、I8、F4、F8 一律不解析。⚠ 後果不是被拒絕，而是「假成功」：以 &lt;F8 102.5&gt; 寫 2760，本機取到空字串、實際寫入 0、並把 0 存進當前配方的 setup.ini，S2F16 仍回 EAC=0 並照樣發 CEID 48 —— tray 起始位置／格距被歸零，而 host 端看到的是完全成功；若同一封包還有其他 pair，該 F8 item 未被消耗會使後續解析失敗，其餘 pair 全部丟棄並回 EAC=1。正確寫法：2758-2761(F8，mm)與 2762 / 2763(I4)都以 ASCII 送，例 &lt;L,2 &lt;U4 2760&gt; &lt;A '102.5'&gt;&gt;；純整數的 2762 / 2763 亦可用 I1 / I2 / I4 / U1 / U2 / U4。⚠ 此點與 HT-9046 不同：9046 的 S2F15 有 F4 / F8 的解析分支，貴端若沿用 9046 的寫入程式碼打到本機就會踩到本項。本方認定為缺陷，將於下一批次改為「ECV 依該 EC 宣告的型別解析；不認得的型別回 EAC=1 並記錄，絕不以 0 代替」。</t>
+(2)〔2026-08-04 追加項後實測〕EAC：0=整包受理並寫入 / 1=封包格式錯誤、ECV 型別本機讀不出、或含不可寫的號碼(唯讀的 1501 與所有未登錄號碼) / 2=機台忙碌(運轉中或機內有 IC)且封包內含 tray 幾何 / 3=值本身不可用(1007 空字串，或 tray 幾何送了無法轉為數值的值)。⚠ 本機自 2026-08-04 起為「全有全無」：先整包檢查，任一筆不通過就整包拒絕、完全不寫入、也不發 CEID 48；只有整包 EAC=0 時才逐筆寫入並發一次 CEID 48。實測：{1006,1007} 回 EAC=1 且 Operator ID 維持原值；{1007 空字串, 2760 有效值} 回 EAC=3 且 tray 值不變。⚠ 若貴端機台仍在 2026-08-04 之前的韌體，行為不同 —— 該版是逐筆立即套用，混合封包會「已寫入卻回報失敗」(詳見「2026-08-04 第 5 版修訂」第 22 項)。多筆 EAC 的優先序為 1 &gt; 3 &gt; 2，因此收到 2 才代表「等機台閒下來重送即可成功」。
+(3)〔2026-08-04 追加項後實測〕S2F30 回報的 ECMIN / ECMAX 為零長度(未宣告，與 HT-90XX 相同)，本機不做數值範圍檢查(不會擋超出機構行程的值)，但會做「可否轉為數值」檢查：2758-2761 需可轉為浮點數、2762 / 2763 需可轉為整數，否則回 EAC=3 並整包不寫入。實測 ASCII 'abc' 寫 2760：EAC=3、值不變。⚠ 舊版韌體會把它當 0 寫入並存進配方檔且仍回 EAC=0。
+(4)〔2026-08-04 實測〕未登錄的 ECID：S2F30 回 L,6 但名稱 / 三個界限 / 單位皆為零長度；S2F14 回一個零長度項目；S2F15 一律不寫入並回 EAC=1(整包拒絕)。
+(5)〔2026-08-04 追加項後實測〕S2F15 的 ECV 型別：本機可解析 ASCII、F8、F4、BOOLEAN 與 U1 / U2 / U4 / I1 / I2 / I4，因此貴端可以直接用本表「型別」欄的型別送(例 &lt;L,2 &lt;U4 2760&gt; &lt;F8 71.5&gt;&gt;)，也可以一律用 ASCII(例 &lt;L,2 &lt;U4 2760&gt; &lt;A '71.5'&gt;&gt;)，兩者等效。不可解析的型別(BINARY、U8、I8)回 EAC=1 並整包不寫入 —— 不會再以 0 代替。⚠ 舊版韌體(2026-08-04 之前)只認 ASCII 與 U1-U4 / I1-I4：F8 / F4 會被當空字串、實際寫入 0、卻仍回 EAC=0 並發 CEID 48(tray 幾何被歸零而 host 端看到成功)。若貴端機台尚未更新韌體，請務必只用 ASCII 送 ECV。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="69" min="1" max="1"/>
@@ -933,7 +933,7 @@
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>2026-07-29 (第 1 版) / 2026-07-30 (第 2 版) / 2026-08-02 (第 3 版) / 2026-08-03 (第 4 版) / 2026-08-03 (第 4 版 追加項、追加項2、追加項3、追加項4、追加項5) / 2026-08-04 (第 5 版，本次)</t>
+          <t>2026-07-29 (第 1 版) / 2026-07-30 (第 2 版) / 2026-08-02 (第 3 版) / 2026-08-03 (第 4 版) / 2026-08-03 (第 4 版 追加項、追加項2、追加項3、追加項4、追加項5) / 2026-08-04 (第 5 版、第 5 版 追加項、追加項2) / 2026-08-04 (第 6 版，本次)</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       <c r="B6" s="49" t="inlineStr">
         <is>
           <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (commit bd1d785)
-〔20260804 更正：本欄的 commit bd1d785 是第 1 版(2026-07-29)的韌體，其中並沒有第 2 版之後的任何一項(SVID 4 / 9、1007、1259-1261、38199-38201、CEID 276-292 皆不在其中)。各版次的韌體基準請以該版自身的「依據韌體」欄為準；本檔目前內容依同一 branch 的第 4 版 追加項1~5 與本第 5 版。〕</t>
+〔20260804 更正：本欄的 commit bd1d785 是第 1 版(2026-07-29)的韌體，其中並沒有第 2 版之後的任何一項(SVID 4 / 9、1007、1259-1261、38199-38201、CEID 276-292 皆不在其中)。各版次的韌體基準請以該版自身的「依據韌體」欄為準；本檔目前內容依同一 branch 的第 4 版 追加項1~5、第 5 版與其追加項1~2，以及第 6 版(66xxx 全數下架 + SVID 1008 + 1006 多批串接 + Report 1 對齊，見第 31-33 項)。〕</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       <c r="B11" s="49" t="inlineStr">
         <is>
           <t>補上 1518 Real/Dummy(本機已註冊，原表漏列)。本機共註冊 51 個 SVID。
-〔20260804 現況：本機共註冊 76 個 SVID(第 1 版為 51)。本檔 SVID 工作表的 76 列即為 2026-08-04 實測 S1F11 &lt;L[0]&gt; 回覆的內容，逐號相符。〕</t>
+〔20260804 第 6 版現況：本機共註冊 67 個 SVID(第 1 版為 51，第 5 版為 76；第 6 版下架 66xxx 十個、新增 1008，故 76 - 10 + 1 = 67)。本檔 SVID 工作表的 67 列即為 2026-08-04 第 6 版建置實測 S1F11 &lt;L[0]&gt; 回覆的內容，逐號相符。〕</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B21" s="49" t="inlineStr">
         <is>
-          <t>(2026-08-02 已回答，結論與原假設相反)2026-07-31 現場 log 證實貴端 host 確實會對 HT-160S 送 S2F33 / S2F35。且貴端的 S2F35 是「取代」而非「疊加」—— provision 完成後韌體預設的 Report 1 會從事件酬載中消失(當日 CEID 27 由 13 格有值退化為 1 格)，因此原本寫的「保留本機預設」不會發生。AMR 事件(CEID 272-275)在貴端自己的 RPTID 2000(7/7)與 2001(15/15)下覆蓋完整；需留意的是同時綁在這些事件上的 RPTID 502，本機於 2026-08-02 當時只填得出 4 格〔20260804 更新：2026-08-03 補上 3 GemClock、1501 Setup File、1007 Operator ID 後已為 7/8，仍為空值的只剩 1513 Tester On/Off〕(見下一列)。</t>
+          <t>(2026-08-02 已回答，結論與原假設相反)2026-07-31 現場 log 證實貴端 host 確實會對 HT-160S 送 S2F33 / S2F35。且貴端的 S2F35 是「取代」而非「疊加」—— provision 完成後韌體預設的 Report 1 會從事件酬載中消失(當日 CEID 27 由 13 格有值退化為 1 格)〔20260804 第 6 版補註：該次觀察的「13 格」是當時的預設 Report 1。自第 6 版起預設 Report 1 本身就只有 1 格(1027 System Time)，故「退化」一詞已不適用 —— provision 前後都是 1 格，只是內容由時間戳換成貴端定義的欄位。詳見第 33 項〕，因此原本寫的「保留本機預設」不會發生。AMR 事件(CEID 272-275)在貴端自己的 RPTID 2000(7/7)與 2001(15/15)下覆蓋完整；需留意的是同時綁在這些事件上的 RPTID 502，本機於 2026-08-02 當時只填得出 4 格〔20260804 更新：2026-08-03 補上 3 GemClock、1501 Setup File、1007 Operator ID 後已為 7/8，仍為空值的只剩 1513 Tester On/Off〕(見下一列)。</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,8 @@
       </c>
       <c r="B22" s="49" t="inlineStr">
         <is>
-          <t>(2026-08-02 更新)RPTID 502 = {1006, 1007, 1011, 3, 1501, 1517, 1518, 1513}，貴端將它綁在 23 個 CEID 上(1、9、10、13、14、15、19、26、27、34、42、44、45、48、49、50、73、76、80、272、273、274、275)，含當日流量最高的 CEID 27、CEID 1 Start Pressed，以及 272/273/274/275 四個 AMR 事件。本機可填的格數已由 1/8(僅 1518)提升為 7/8〔20260804 更新：2026-08-02 時為 4/8(1006、1011、1517、1518)，2026-08-03 補上 3 GemClock、1501 Setup File、1007 Operator ID 後為 7/8〕。此事不需要 9045 的 SVID 目錄即可完成 —— 1517 是靠 9045 自身的 EC 宣告解出來的。〔20260804 更新〕仍為空值的只剩 1 格：1513 Tester On/Off(HT-160S 為 Tray Sorter，機構上無測試機構，建議自報表定義中移除或接受空值)。原列為待確認的 1007 Operator ID、3 GemClock、1501 Setup File 均已於 2026-08-03(第 4 版與追加項4)實作，請保留在報表定義中。另 RPTID 501 目前為 5/12(1101 Loader Count、1102 Output Total Count、1103-1105 Auto1-3 Count)、RPTID 508 為 2/6(1021 UPH、1009 Lot Start Time)、RPTID 517 為 1/1(37010)。〔20260804 更新：本欄原記 501=2/12、508=1/6，係 2026-08-02 的數字。〕</t>
+          <t>(2026-08-02 更新)RPTID 502 = {1006, 1007, 1011, 3, 1501, 1517, 1518, 1513}，貴端將它綁在 23 個 CEID 上(1、9、10、13、14、15、19、26、27、34、42、44、45、48、49、50、73、76、80、272、273、274、275)，含當日流量最高的 CEID 27、CEID 1 Start Pressed，以及 272/273/274/275 四個 AMR 事件。本機可填的格數已由 1/8(僅 1518)提升為 7/8〔20260804 更新：2026-08-02 時為 4/8(1006、1011、1517、1518)，2026-08-03 補上 3 GemClock、1501 Setup File、1007 Operator ID 後為 7/8〕。此事不需要 9045 的 SVID 目錄即可完成 —— 1517 是靠 9045 自身的 EC 宣告解出來的。〔20260804 更新〕仍為空值的只剩 1 格：1513 Tester On/Off(HT-160S 為 Tray Sorter，機構上無測試機構，建議自報表定義中移除或接受空值)。原列為待確認的 1007 Operator ID、3 GemClock、1501 Setup File 均已於 2026-08-03(第 4 版與追加項4)實作，請保留在報表定義中。另 RPTID 501 目前為 5/12(1101 Loader Count、1102 Output Total Count、1103-1105 Auto1-3 Count)、RPTID 508 為 2/6(1021 UPH、1009 Lot Start Time)、RPTID 517 為 1/1(37010)。〔20260804 更新：本欄原記 501=2/12、508=1/6，係 2026-08-02 的數字。〕
+〔20260804 第 6 版重要提醒：本報表第 1 格的 SVID 1006 回值定義已改變 —— 現在回「機上所有批號以半角逗號串接」。單批生產時與舊值逐位元組相同，貴端無需改動；但多批同時在機時該格會是 "LOTA,LOTB" 這樣的字串。報表的格數、順序與型別(A)完全不變。詳見第 32 項。〕</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2165,7 @@
       <c r="B116" s="71" t="inlineStr">
         <is>
           <t>**ECID 1006 Lot ID 是否開放貴端以 S2F15 寫入?**
-本機現況(2026-08-04 實測)：1006 只註冊在 SV 命名空間，可由 S1F3 與報表讀取，未註冊為 EC。⚠ 其回值的定義請一併注意：批已開時回閂鎖的作用中批號，批未開時回主畫面批號輸入欄當下的文字。貴端若對本機送 S2F15 ECID 1006：機台閒置時回 EAC=1(非可寫常數)、運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況該批號字串都直接丟棄 —— 不寫入任何欄位、不改變 SVID 1006 的回值、不發 CEID 48。
+本機現況(2026-08-04 實測)：1006 只註冊在 SV 命名空間，可由 S1F3 與報表讀取，未註冊為 EC。⚠ 其回值的定義請一併注意〔20260804 第 6 版更新〕：機上有批時回「所有批號以半角逗號串接」(單批 = 該批號本身，與舊行為相同)，批未開時回主畫面批號輸入欄當下的文字。詳見第 31 項。貴端若對本機送 S2F15 ECID 1006：機台閒置時回 EAC=1(非可寫常數)、運轉中或機內尚有 IC 時回 EAC=2(忙碌)；兩種情況該批號字串都直接丟棄 —— 不寫入任何欄位、不改變 SVID 1006 的回值、不發 CEID 48。
 ⚠ 請一併注意封包形狀的問題：貴端 2026-06-08 是把 1006 與 1007 包在同一個 S2F15 裡，該形狀在本機會造成「1007 寫入成功、整包卻回 EAC=1 且不發事件」(見本版第 22 項)。
 HT-90XX 的作法(供對照)：其 ECID 1006 綁在機台的系統批號輸入欄，寫入即成為機台的批號身分(UPH 檔名、2D 分選清單檔名、送測試機的 INNER_LOT_ID 皆取自該欄)；寫入不受 GEM 控制狀態限制，但整包 S2F15 在「機內有 IC」時一律回 EAC=2 且完全不寫入。⚠ 另請注意 9045 的兩層批號在 SECS 上是「各用一個 ECID」，並非只有 1006：ECID 1006 寫的是系統批號，客戶批號另有 ECID 1583 Lot Information Customer Lot ID —— 貴端的 HT-9046LS 與 HT-9011UC 皆有登錄(以 S2F29 全查即可看到)，該值就是 9045 畫面上的客戶批號。另有 ECID 1582 Lot Information Inner Lot ID，但它是系統批號的鏡像，並非第三層批號。因此若貴端需要同時設定兩層批號，可比照 9045 各用一個號碼(1006 系統批號、1583 客戶批號)，不必把兩層批號擠在同一個 ECID —— 請於下列 (b) 一併裁定是否要求本機也登錄 1583(本機的客戶批號目前來源為貴端 WebAPI，逐顆 IC 記錄於 Soter 第 6 欄)。
 ⚠ 另有一處需請貴端一併確認：貴端提供的 SECS 規格書(SECS_20240826.xlsx「SV &amp; EC」)中，1006 這一列的機種支援欄是空白的(1007、1501、2758-2763、16000/16002/16023/16026、35011、37007 都標 V)，也就是規格書本身並未把 1006 列為 HT-90XX 家族支援的號碼；但兩棵 HT-90XX 原始碼都確實登錄了它，且貴端 host 當天也真的寫了三次。請一併釐清以哪一份為準。
@@ -2394,6 +2395,116 @@
           <t>1. 810 與 899 的 SECSGEM/uHGemHT9045_SV.cpp 全文關鍵字掃描(Run Mode/Running/Alarm/Sort/Lot Count/Current Lot)：相關 SV 註冊皆不存在，僅 1033 Running Time、2015-2017 Contact Alarm 設定、15500 Pre Alarm Message、38830 2DID yield 布林等不同義項目。
 2. 家族大統整 SV&amp;EC 目錄(9,796 列)逐列掃描：同名／近義候選僅 1008、35530、40015 三個，語意逐一排除(見第 30 項)。
 3. _manual.xlsx 與本檔以 openpyxl 逐格 diff：59 格差異全數列於第 29 項，無內容性差異。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="58" t="inlineStr">
+        <is>
+          <t>2026-08-04 第 6 版修訂 Revision 6</t>
+        </is>
+      </c>
+      <c r="B136" s="72" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="59" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B137" s="71" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (66xxx 自有段全數下架 + 新增 SVID 1008 + SVID 1006 改為多批串接 + 預設 Report 1 對齊 HT-90XX)。本版為程式碼變更，不是文件版本。建置：模擬版 -Clean exit 0；註銷 SOFT_SIMULATE 之真機版 -Full exit 0；還原後再 -Full exit 0；原始碼編碼檢查 166 檔通過。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="59" t="inlineStr">
+        <is>
+          <t>⚠ 31. HT-160S 自有段 66xxx 十個 SVID 全數下架(本版最大變更，breaking change)</t>
+        </is>
+      </c>
+      <c r="B138" s="71" t="inlineStr">
+        <is>
+          <t>貴端 2026-08-04 裁定：HT-160S 一律只公佈 HT-90XX 家族編號，自有段不再保留。第 5 版 追加項2 第 30 項曾主張其中八個「家族無同義號碼故必須自定義」、另兩個「因預設 Report 1 形狀已凍結故保留」—— 本版依貴端裁定全部下架，第 30 項的結論即以本項取代(該項作為當時的評估紀錄保留，不予改寫)。十個號碼與其替代路徑逐一如下：
+• 66000 Run Mode → 改用家族 SVID 1008 Run Mode(ASCII，本機恆回 "0" = Normal)。⚠ 請注意資訊落差：1008 的家族值域是「0:Normal / 1:RT / 2:EQC」(測試流程模式)，本機為分選機、無重測也無 EQC，故恆為 0；原 66000 帶的是機台任務模式(0=Normal / 1=Home / 2=OneCycle / 3=CleanOut / 4=TrayFeed)，此資訊自本版起不再由任何 SVID 公佈，請改讀 SVID 1011 Machine State 或追蹤任務類 CEID(3 / 4 按下、41 / 42 完成)。HT-90XX 亦是如此。
+• 66001 System Running → 無替代號碼。是否在運轉請由 SVID 1011 的狀態文字與 CEID 1 Start / 2 Pause 判定。HT9046LS V3.32.810 與 HT9011UC V3.33.899 皆未註冊同義 SVID。
+• 66002 Control State → 改讀 SVID 4 GemControlState(與 9 PreviousGemControlState)，值域為 HT9045 的 1=Off-Line / 2=On-Line Local / 3=On-Line Remote。本機內部仍以 GEM 標準值域 1/4/5 保存同一個狀態，但不再對外公佈該編號。
+• 66010 Alarm Active / 66011 Alarm Code → 無替代號碼。警報一律走 S5F1(目錄走 S5F6)，與 HT9045 相同；810 / 899 亦無任何「目前警報」SV。
+• 66020 Total IC → 改讀 SVID 1101 Loader Count(自 Loader 盤取起的 IC 數)與 SVID 1102 Output Total Count(已放入 Bin 的 IC 數)。原 66020 是本機第三個計數器(本批已處理總數)，家族無此概念。
+• 66021 Total Sorted → 改讀 SVID 1102 Output Total Count。兩者本來就綁同一個計數器(MachineRun.iTotalSorted)，值完全相同，屬純去重。
+• 66030 Active Lot Count / 66031 Current Lot ID → 改由 SVID 1006 Lot ID 承接，見第 32 項。
+• 66032 Sort Mode → 無替代號碼。家族沒有分選模式 SVID(唯一近似的 35530 "[I27] Manual sort mode" 是 HT9045/46 的 BOOLEAN 機台選項，型別與語意皆不合)。⚠ 明確接受的能力損失：貴端仍可用 S2F41 LOTSTART 的 SORTMODE 參數「設定」分選模式(行為完全未變)，但自本版起無法再用 S1F3「回讀」確認；若貴端需要回讀，請配發一個家族編號給本方。
+⚠ 這十個號碼自本版起為永久空號，本方永不挪用。舊 host 若仍綁著它們，S1F3 / 報表該格回空 list item &lt;L[0]&gt;，list 長度不變、後續欄位不位移 —— 且 &lt;L[0]&gt;(位元組 01 00)與「已註冊但字串為空」的 &lt;A[0]&gt;(位元組 41 00)在線上可區分，故這是可偵測的空白，不是無法察覺的錯值。本機共註冊 SVID 數 76 → 67。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="59" t="inlineStr">
+        <is>
+          <t>⚠ 32. SVID 1006 Lot ID 改為「機上所有批號以逗號串接」(取代 66030 / 66031)</t>
+        </is>
+      </c>
+      <c r="B139" s="71" t="inlineStr">
+        <is>
+          <t>貴端 2026-08-04 指定以半角逗號(,)為分隔符，不加空白。
+• 單批：回該批號本身，例如 "PROBE_LOT_A" —— 與本版之前逐位元組相同。這是刻意的：貴端持久化的 RPTID 502 第 1 格就是 1006，單批生產時貴端的解析完全不需改動。
+• 多批：依註冊順序串接，例如 "PROBE_LOT_A,PROBE_LOT_B,PROBE_LOT_C"。
+• 由此回推被下架的兩個號碼：批數 = 逗號數 + 1(原 66030)；首批 = 第一個逗號前的字串(原 66031)。
+• 未開批(批次登錄表為空)：回主畫面批號輸入欄當下的文字 —— 與既有公佈的契約相同，未變更。
+• 已被移除的批次會留下空槽位(其他模組持有槽位索引，故不能重排)，串接時一律跳過空槽，因此不會出現開頭逗號或連續逗號。
+⚠ 請貴端確認兩件事：(1) 京元批號本身不含半角逗號 —— 若含，串接後無法唯一切割，請改用其他分隔符；(2) 貴端 RPTID 502 第 1 格的解析在多批生產時要能接受逗號串。型別仍為 A、報表格數與順序完全不變。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="59" t="inlineStr">
+        <is>
+          <t>⚠ 33. 預設 Report 1 改為僅 {1027 System Time}，與 HT-90XX 完全相同</t>
+        </is>
+      </c>
+      <c r="B140" s="71" t="inlineStr">
+        <is>
+          <t>原本 Report 1 帶 13 個 SV(1001 / 1003 / 1021 / 1027 + 九個 66xxx)。其中九個隨第 31 項消失，留下四格的殘缺形狀既不是舊形狀也不是家族形狀，因此本版直接對齊家族：HT9045 的 AddReprot 只定義 ReportIDContent[]={1027}，貴端自己的 HT9046 持久化檔 EventReport_ReportID.def 也只有一列(RPTID 1, Type 1, SVID 1027)。本機自本版起與兩者一致。
+• 影響範圍：292 個 CEID 中有 288 個連結 Report 1(僅 272-275 另連 Report 2/6、3、4/6、7 供 AMR 交握)，故幾乎每一筆 S6F11 的酬載都變成一格；S1F24 Event Namelist 走同一條 CEID→Report→SVID 鏈，那 288 列也由 13 個 VID 縮為 1 個。
+• Report 2-7(AMR P1-P9 bitmap、各站盤數/件數、身分盤 2D)完全未動 —— 272-275 交握的形狀、欄位數、順序、型別皆不變。
+• 貴端若已用 S2F33 + S2F35 定義並連結自己的報表(貴端自 2026-06 起即如此，本機 system\EventReportDef.ini 記錄到 Report=501 / 502 / 513 / 800)，本變更對貴端的事件內容毫無影響 —— 貴端的連結會完全取代 Report 1。
+⚠ 唯一的實質退化，請務必納入貴端的復電程序：S2F35 的「事件→報表」連結是 session-only、本機不做持久化(持久化檔只存 Report= 的報表定義)，所以每次電源循環後這 288 個 CEID 都會退回 Report 1，直到貴端重新送出 S2F33 + S2F35。本版之前那個空窗期還能收到 13 個機況 SV，本版之後只會收到時間戳。若貴端希望空窗期仍有機況資料，兩條路可選：(a) 復電後儘早重下 provisioning；(b) 由本方在預設 Report 1 內加回幾個家族號碼(例如 1001 / 1003 / 1011 / 1021)—— 請貴端裁定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="59" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B141" s="71" t="inlineStr">
+        <is>
+          <t>CEID 的編號、語意與發射點(292 個號碼、57 個發射點)全部未變；S5 警報目錄(481 筆)未變；EC 的號碼、名稱、型別、可寫範圍(1007 與 2758-2763)全部未變；S1F17 / S2F29 / S2F30 / S2F13 / S2F15 的回覆形狀未變；Report 2-7 的內容與 272-275 的交握形狀未變；Soter 輸出檔契約未變。機台的機構行為、計數行為與數值全部未變 —— 本版只改變「哪些號碼對外公佈」與「預設報表帶哪些格子」。被下架的 66022-66027、66033(先前版本已移除)仍為空號，一併永不挪用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="59" t="inlineStr">
+        <is>
+          <t>第 6 版的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B142" s="71" t="inlineStr">
+        <is>
+          <t>1. 建置：模擬版 -Clean exit 0；註銷 SOFT_SIMULATE 之真機版 -Full exit 0；還原 SOFT_SIMULATE 後再 -Full exit 0；scripts/ops/check-ht160s-source-encoding.ps1 通過(166 檔)。
+2. 以 headless SECS host 對重新建置的實機(EXE\ht160s.exe)做 HSMS round-trip 實測，13 項全數通過：
+  (A) S1F3 查十個已下架號碼 → 十格皆回 &lt;L[0]&gt;，list 長度不變；
+  (B) SVID 1008 → &lt;A[1] '0'&gt;；
+  (C) 替代號碼皆有實值：4 → &lt;U1 3&gt;、1011 → &lt;A 'HALT'&gt;、1101 / 1102 → I4、1021 → I4 89、1027 → 19 字元時間戳；
+  (D) S1F11 &lt;L[0]&gt; 目錄 = 67 個 SVID，十個已下架號碼皆不在其中、1008 在其中；
+  (E) 線上事件 CEID 6 / 8 / 27 / 93 / 141 的 Report 1 皆為 L[1]{&lt;A 19 字元時間戳&gt;}，剛好一格；
+  (F/G/J) 1006：單批回 'PROBE_LOT_A'、兩批回 'PROBE_LOT_A,PROBE_LOT_B'、三批依序全串接；
+  (K) CLEAR_LOT_INFO 後 1006 回到測試前的基準值(空字串)，證明未開批的既有契約未變；
+  (H) &lt;L[0]&gt;(未註冊)與 &lt;A[0]&gt;(已註冊但空)在線上可區分 —— 同一封包內 66031 → L,0 而 1006 → A,0；
+  (I) AMR 的 38219 / 38220 / 38221 / 38204 / 38222 仍註冊且型別正確，證明 Report 2-7 未受影響。
+3. 三方查證(推翻第 30 項的依據)：810 與 899 兩套 HT90XX 原始碼全文、家族大統整 SV&amp;EC 目錄 9,796 列、本機 RefreshSVData 綁定逐行。1008 在家族大表為 SV / ASCII / "0:Normal; 1:RT; 2:EQC"，標記於 HT-9040S / HT-704X / HT-2036 / HT-2000M(HT9045/46 欄為空、810 與 899 皆未實作)—— 本機依貴端裁定仍採用該號碼並恆回 0。</t>
         </is>
       </c>
     </row>
@@ -2967,25 +3078,14 @@
     &lt;L [1] 
       &lt;L [2] 
         &lt;U4 [1] 1&gt;
-        &lt;L [13] 
-          &lt;A [6] 'HT160S'&gt;
-          &lt;A [7] '1.0.0.0'&gt;
-          &lt;I4 [1] 886&gt;
-          &lt;A [19] '2026/07/23 16:44:31'&gt;
-          &lt;I4 [1] 0&gt;
-          &lt;I4 [1] 1&gt;
-          &lt;I4 [1] 0&gt;
-          &lt;I4 [1] 0&gt;
-          &lt;I4 [1] 0&gt;
-          &lt;I4 [1] 189&gt;
-          &lt;I4 [1] 9&gt;
-          &lt;I4 [1] 5&gt;
-          &lt;A [10] 'SIMU_LOT_A'&gt;
+        &lt;L [1] 
+          &lt;A [19] '2026/08/04 15:49:53'&gt;
         &gt;
       &gt;
     &gt;
   &gt;
-.</t>
+.
+〔20260804 第 6 版：本範例已更新。預設 Report 1 自本版起僅含 SVID 1027 System Time 一格 —— 與 HT-90XX 出廠預設完全相同。上一版的 &lt;L [13]&gt; 範例(HT160S / 1.0.0.0 / UPH / 時間 + 九個 66xxx 值)已不適用，該九個號碼已下架，詳見第 31 項。本形狀為 2026-08-04 以 headless SECS host 對實機實測所得(CEID 6 / 8 / 27 / 93 / 141 逐筆確認)。⚠ 貴端若已用 S2F33 / S2F35 定義自己的報表並連結事件，本變更對貴端無影響 —— 貴端的連結會完全取代 Report 1。〕</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3201,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>[20260729] 已實作(2026-07-29 新增)。CEID 27 Change Machine State：機台狀態文字每次變更即送 S6F11(RUNNING / PAUSE / EMG / LOCK / SAFE DOOR / AIR / MOTOR OFF / Clean Out / One Cycle …)。另 SVID 66000 RunMode、66001 SystemRunning 可主動查詢。
+          <t>[20260729] 已實作(2026-07-29 新增)。CEID 27 Change Machine State：機台狀態文字每次變更即送 S6F11(RUNNING / PAUSE / EMG / LOCK / SAFE DOOR / AIR / MOTOR OFF / Clean Out / One Cycle …)。另 SVID 66000 RunMode、66001 SystemRunning 可主動查詢。〔20260804 第 6 版更正：66000 與 66001 已下架。機況請一律讀 SVID 1011 Machine State(值域見下段)；「是否在運轉」由 1011 的狀態文字與 CEID 1 Start / 2 Pause 判定。另新增 SVID 1008 Run Mode，但本機恆回 "0"(Normal)，不帶機台任務模式資訊。詳見第 31 項。〕
 [20260802] 另新增 SVID 1011 Machine State，內容與上述狀態文字完全相同(HT9045 對應號)，可用 S1F3 主動查詢。值域：HALT / INIT / HOMING / Clean Out / Tray Feed / One Cycle / RUNNING / LOCK / EMG / MOTOR OFF / SAFE DOOR / AIR / PAUSE。
 [20260803] 補充資料來源：此事件的「機況」值即 SVID 1011 Machine State(2026-08-01 新增)。貴端若以自訂報表(S2F33/S2F35)接收此事件，請將 1011 納入該報表，否則事件本身雖會送出、對應欄位仍為空 item —— 這正是貴端 2026-08-03 來信第 2 點的成因，詳見「2026-08-03 第 4 版修訂」。</t>
         </is>
@@ -3189,7 +3289,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>[20260803 追加項2 改版] 已實作。開批時刻由 SVID 1009 Lot Start Time 公佈，格式為 HT9045 線上格式 'yyyy-mm-dd hh:nn:ss'(破折號)。⚠ 2026-07-30 至 2026-08-03 之間本機另以自有的 SVID 66033 公佈同一個值(斜線格式)，該號碼已於 2026-08-03 移除(與 1009 重複)，請改讀 1009。以下行為全部由 1009 承接，未變更:於 Lot Start 當下閂鎖 — 操作面板 Lot Start 按鈕與 SECS S2F41 LOTSTART 兩條路徑都會寫入 — Lot End 清空，貨批進行中可隨時以 S1F3 回查(不會隨系統時間變動)。CEID 6 Lot Start 事件照舊發送，可作為即時通知。註1：1009 未加入預設 Report 1。該報表是每個 CEID 的預設酬載，其 13 個 SV 的內容已對貴端公布，加欄位會改變線上每一筆事件的長度；若需在事件內帶出起測時間，請以 S2F33 / S2F35 將 1009 綁進貴端自訂報表即可。註2：[20260802 更正] 本欄位會隨工單一起持久化，第 2 版所述「不做斷電保存」已不適用。Lot Start 當下除了閂鎖開批時刻，也會把同一個時間戳寫入工單中繼檔；機台中途重開後，若操作員選擇「沿用上一張工單」，1009 會以原始時間戳回填(不是復電時刻，也不是本次開機時間)，該貨批仍視為進行中。若操作員選擇「重新開始」、或該工單建立於本功能之前、或中繼檔讀寫失敗，則 1009 為空。Lot End 一律清空開批時刻並刪除中繼檔。
+          <t>[20260803 追加項2 改版] 已實作。開批時刻由 SVID 1009 Lot Start Time 公佈，格式為 HT9045 線上格式 'yyyy-mm-dd hh:nn:ss'(破折號)。⚠ 2026-07-30 至 2026-08-03 之間本機另以自有的 SVID 66033 公佈同一個值(斜線格式)，該號碼已於 2026-08-03 移除(與 1009 重複)，請改讀 1009。以下行為全部由 1009 承接，未變更:於 Lot Start 當下閂鎖 — 操作面板 Lot Start 按鈕與 SECS S2F41 LOTSTART 兩條路徑都會寫入 — Lot End 清空，貨批進行中可隨時以 S1F3 回查(不會隨系統時間變動)。CEID 6 Lot Start 事件照舊發送，可作為即時通知。註1：1009 未加入預設 Report 1。〔20260804 第 6 版更正：原本的理由是「該報表的 13 個 SV 已對貴端公布，加欄位會改變每一筆事件的長度」。自本版起 Report 1 已改為僅 SVID 1027 System Time 一格(對齊 HT-90XX)，該理由不再適用，但結論不變 —— 1009 仍不在預設報表內。〕若需在事件內帶出起測時間，請以 S2F33 / S2F35 將 1009 綁進貴端自訂報表即可。註2：[20260802 更正] 本欄位會隨工單一起持久化，第 2 版所述「不做斷電保存」已不適用。Lot Start 當下除了閂鎖開批時刻，也會把同一個時間戳寫入工單中繼檔；機台中途重開後，若操作員選擇「沿用上一張工單」，1009 會以原始時間戳回填(不是復電時刻，也不是本次開機時間)，該貨批仍視為進行中。若操作員選擇「重新開始」、或該工單建立於本功能之前、或中繼檔讀寫失敗，則 1009 為空。Lot End 一律清空開批時刻並刪除中繼檔。
 [20260803 追加項2] 依「相同功能使用同一編號」的原則，本機自有的 66033 已移除，開批時刻自此只由 SVID 1009 公佈。66033 保留空號、不再挪作他用；貴端設定若未更新，該欄位會回空 item(未知 SVID)，長度不變、不會位移到別的資料上。</t>
         </is>
       </c>
@@ -3271,7 +3371,7 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>[20260729] HT-160S 為 Tray Sorter，無測試機構，故無測試結果。分選結果以 SVID 66021 Total Sorted、各 Bin 分選數與 Production log / Soter CSV 提供。</t>
+          <t>[20260729] HT-160S 為 Tray Sorter，無測試機構，故無測試結果。分選結果以 SVID 1102 Output Total Count、各 Bin 分選數與 Production log / Soter CSV 提供。〔20260804 第 6 版更正：原寫 SVID 66021 Total Sorted，該號碼已下架；1102 綁的是同一個計數器(值完全相同)，請改讀 1102。詳見第 31 項。〕</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.5" bestFit="1" customWidth="1" style="69" min="1" max="1"/>
@@ -3948,682 +4048,592 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="44" t="n">
+      <c r="A10" s="47" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Run Mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="n">
         <v>1009</v>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Lot Start Time</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="47" t="n">
+    <row r="12">
+      <c r="A12" s="47" t="n">
         <v>1011</v>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>Machine State</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>1021</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>UPH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>UPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
         <v>1027</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>System Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="47" t="n">
-        <v>1101</v>
-      </c>
-      <c r="B14" s="47" t="inlineStr">
-        <is>
-          <t>Loader Count</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="47" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>Loader Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="n">
         <v>1102</v>
       </c>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>Output Total Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="44" t="n">
-        <v>1103</v>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>Auto1 Count</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="44" t="n">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B17" s="44" t="inlineStr">
         <is>
-          <t>Auto2 Count</t>
+          <t>Auto1 Count</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="44" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>Auto3 Count</t>
+          <t>Auto2 Count</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="44" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>Auto3 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n">
         <v>1259</v>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>Auto4 Count</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="47" t="n">
+    <row r="21">
+      <c r="A21" s="47" t="n">
         <v>1260</v>
       </c>
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>Auto5 Count</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="46" t="n">
+    <row r="22">
+      <c r="A22" s="46" t="n">
         <v>1261</v>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Auto6 Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="44" t="n">
-        <v>1501</v>
-      </c>
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>Setup File</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="44" t="n">
-        <v>1517</v>
+        <v>1501</v>
       </c>
       <c r="B23" s="44" t="inlineStr">
         <is>
-          <t>Start Mode</t>
+          <t>Setup File</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="44" t="n">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Real/Dummy</t>
+          <t>Start Mode</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="44" t="n">
-        <v>2758</v>
+        <v>1518</v>
       </c>
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Type 1 Tray Pitch X</t>
+          <t>Real/Dummy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="44" t="n">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="B26" s="44" t="inlineStr">
         <is>
-          <t>Type 1 Tray Pitch Y</t>
+          <t>Type 1 Tray Pitch X</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="44" t="n">
+        <v>2759</v>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>Type 1 Tray Pitch Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="n">
         <v>2760</v>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>Type 1 Tray Start Position X</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="47" t="n">
+    <row r="29">
+      <c r="A29" s="47" t="n">
         <v>2761</v>
       </c>
-      <c r="B28" s="47" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>Type 1 Tray Start Position Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>2762</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Type 1 Tray Division X</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Type 1 Tray Division Y</t>
+          <t>Type 1 Tray Division X</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>37010</v>
+        <v>2763</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Enter Skip IC Count</t>
+          <t>Type 1 Tray Division Y</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>38199</v>
+        <v>37010</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>AUTO4 Carrier ID</t>
+          <t>Enter Skip IC Count</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>38200</v>
+        <v>38199</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AUTO5 Carrier ID</t>
+          <t>AUTO4 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>38201</v>
+        <v>38200</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>AUTO6 Carrier ID</t>
+          <t>AUTO5 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>38202</v>
+        <v>38201</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Loader Carrier ID</t>
+          <t>AUTO6 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>38203</v>
+        <v>38202</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Empty Carrier ID</t>
+          <t>Loader Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>38204</v>
+        <v>38203</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Color Carrier ID</t>
+          <t>Empty Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>38205</v>
+        <v>38204</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>AUTO1 Carrier ID</t>
+          <t>Color Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>38206</v>
+        <v>38205</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>AUTO2 Carrier ID</t>
+          <t>AUTO1 Carrier ID</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
+        <v>38206</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>AUTO2 Carrier ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
         <v>38207</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>AUTO3 Carrier ID</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="32" t="n">
+    <row r="42">
+      <c r="A42" s="32" t="n">
         <v>38219</v>
       </c>
-      <c r="B41" s="33" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>Supplement Bin</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>38220</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>LD UnLD Check AGV</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>38221</v>
+        <v>38220</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>LD UnLD Finish AGV</t>
+          <t>LD UnLD Check AGV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>38222</v>
+        <v>38221</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>AMR Loader Tray Count</t>
+          <t>LD UnLD Finish AGV</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>38223</v>
+        <v>38222</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>AMR Empty Tray Count</t>
+          <t>AMR Loader Tray Count</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>38224</v>
+        <v>38223</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>AMR Color Tray Count</t>
+          <t>AMR Empty Tray Count</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>38225</v>
+        <v>38224</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AMR AUTO1 Tray Count</t>
+          <t>AMR Color Tray Count</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>38226</v>
+        <v>38225</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Tray Count</t>
+          <t>AMR AUTO1 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>38227</v>
+        <v>38226</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Tray Count</t>
+          <t>AMR AUTO2 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>38228</v>
+        <v>38227</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>AMR Loader Device Count</t>
+          <t>AMR AUTO3 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>38229</v>
+        <v>38228</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>AMR Empty Device Count</t>
+          <t>AMR Loader Device Count</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
+        <v>38229</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>AMR Empty Device Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
         <v>38230</v>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>AMR Color Device Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="45" t="n">
-        <v>38231</v>
-      </c>
-      <c r="B53" s="48" t="inlineStr">
-        <is>
-          <t>AMR AUTO1 Device Count</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="45" t="n">
-        <v>38232</v>
+        <v>38231</v>
       </c>
       <c r="B54" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Device Count</t>
+          <t>AMR AUTO1 Device Count</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="45" t="n">
-        <v>38233</v>
+        <v>38232</v>
       </c>
       <c r="B55" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Device Count</t>
+          <t>AMR AUTO2 Device Count</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="45" t="n">
-        <v>38234</v>
+        <v>38233</v>
       </c>
       <c r="B56" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO1 Bin Setting</t>
+          <t>AMR AUTO3 Device Count</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="45" t="n">
-        <v>38235</v>
+        <v>38234</v>
       </c>
       <c r="B57" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO2 Bin Setting</t>
+          <t>AMR AUTO1 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="45" t="n">
-        <v>38236</v>
+        <v>38235</v>
       </c>
       <c r="B58" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO3 Bin Setting</t>
+          <t>AMR AUTO2 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="45" t="n">
-        <v>38237</v>
+        <v>38236</v>
       </c>
       <c r="B59" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Tray Count</t>
+          <t>AMR AUTO3 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="45" t="n">
-        <v>38238</v>
+        <v>38237</v>
       </c>
       <c r="B60" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Tray Count</t>
+          <t>AMR AUTO4 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="45" t="n">
-        <v>38239</v>
+        <v>38238</v>
       </c>
       <c r="B61" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Tray Count</t>
+          <t>AMR AUTO5 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="45" t="n">
-        <v>38240</v>
+        <v>38239</v>
       </c>
       <c r="B62" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Device Count</t>
+          <t>AMR AUTO6 Tray Count</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="45" t="n">
-        <v>38241</v>
+        <v>38240</v>
       </c>
       <c r="B63" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Device Count</t>
+          <t>AMR AUTO4 Device Count</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="45" t="n">
-        <v>38242</v>
+        <v>38241</v>
       </c>
       <c r="B64" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Device Count</t>
+          <t>AMR AUTO5 Device Count</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="45" t="n">
-        <v>38243</v>
+        <v>38242</v>
       </c>
       <c r="B65" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO4 Bin Setting</t>
+          <t>AMR AUTO6 Device Count</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="45" t="n">
-        <v>38244</v>
+        <v>38243</v>
       </c>
       <c r="B66" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO5 Bin Setting</t>
+          <t>AMR AUTO4 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="45" t="n">
-        <v>38245</v>
+        <v>38244</v>
       </c>
       <c r="B67" s="48" t="inlineStr">
         <is>
-          <t>AMR AUTO6 Bin Setting</t>
+          <t>AMR AUTO5 Bin Setting</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="45" t="n">
-        <v>66000</v>
+        <v>38245</v>
       </c>
       <c r="B68" s="48" t="inlineStr">
         <is>
-          <t>Run Mode</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="45" t="n">
-        <v>66001</v>
-      </c>
-      <c r="B69" s="48" t="inlineStr">
-        <is>
-          <t>System Running</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="45" t="n">
-        <v>66002</v>
-      </c>
-      <c r="B70" s="48" t="inlineStr">
-        <is>
-          <t>Control State</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="45" t="n">
-        <v>66010</v>
-      </c>
-      <c r="B71" s="48" t="inlineStr">
-        <is>
-          <t>Alarm Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="36" t="n">
-        <v>66011</v>
-      </c>
-      <c r="B72" s="36" t="inlineStr">
-        <is>
-          <t>Alarm Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="36" t="n">
-        <v>66020</v>
-      </c>
-      <c r="B73" s="36" t="inlineStr">
-        <is>
-          <t>Total IC</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="36" t="n">
-        <v>66021</v>
-      </c>
-      <c r="B74" s="36" t="inlineStr">
-        <is>
-          <t>Total Sorted</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="45" t="n">
-        <v>66030</v>
-      </c>
-      <c r="B75" s="48" t="inlineStr">
-        <is>
-          <t>Active Lot Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="45" t="n">
-        <v>66031</v>
-      </c>
-      <c r="B76" s="48" t="inlineStr">
-        <is>
-          <t>Current Lot ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="45" t="n">
-        <v>66032</v>
-      </c>
-      <c r="B77" s="48" t="inlineStr">
-        <is>
-          <t>Sort Mode</t>
+          <t>AMR AUTO6 Bin Setting</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6466,12 @@
       </c>
       <c r="D79" s="35" t="inlineStr">
         <is>
-          <t>Report 1(韌體預設，13 個 SV，不含 37010)</t>
+          <t>Report 1(韌體預設，自 2026-08-04 起僅 1 個 SV = 1027 System Time，不含 37010)</t>
         </is>
       </c>
       <c r="E79" s="35" t="inlineStr">
         <is>
-          <t>2026-08-02 新增發射點。條件發射，出廠預設不會送 —— 需在 General.ini 的 [SECS] 段加入 AskSkipICCount=1 才啟用(出貨的 General.ini 未含此鍵，等同關閉)。啟用後，操作員在警報畫面以 SKIP 解除警報時會跳出「本盤取出幾顆 IC?」數字輸入框(0-9999)，操作員實際輸入並確認，韌體才先閂鎖 SVID 37010 再送出本事件；按取消則不送(未回答不等於取出 0 顆)。注意：觸發點是「以 SKIP 解除警報」這個動作本身，不限於 Jam 類警報(HT9045 原名為 Jam Skip IC Count，本機語意較廣)。SVID 37010 一律註冊，可隨時以 S1F3 查詢，未曾發生時回 0。韌體預設報表為 Report 1，其中不含 SVID 37010；貴端若要在事件內收到數量，請以 S2F33/S2F35 將 CEID 78 連結至 RPTID 517={37010}(貴端 2026-07-31 的 provisioning 已如此定義，且該連結會存檔，電源循環後仍有效)。</t>
+          <t>2026-08-02 新增發射點。條件發射，出廠預設不會送 —— 需在 General.ini 的 [SECS] 段加入 AskSkipICCount=1 才啟用(出貨的 General.ini 未含此鍵，等同關閉)。啟用後，操作員在警報畫面以 SKIP 解除警報時會跳出「本盤取出幾顆 IC?」數字輸入框(0-9999)，操作員實際輸入並確認，韌體才先閂鎖 SVID 37010 再送出本事件；按取消則不送(未回答不等於取出 0 顆)。注意：觸發點是「以 SKIP 解除警報」這個動作本身，不限於 Jam 類警報(HT9045 原名為 Jam Skip IC Count，本機語意較廣)。SVID 37010 一律註冊，可隨時以 S1F3 查詢，未曾發生時回 0。韌體預設報表為 Report 1(自 2026-08-04 第 6 版起其內容僅 SVID 1027 System Time 一格)，其中不含 SVID 37010；貴端若要在事件內收到數量，請以 S2F33/S2F35 將 CEID 78 連結至 RPTID 517={37010}(貴端 2026-07-31 的 provisioning 已如此定義，且該連結會存檔，電源循環後仍有效)。</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11426,7 @@
       </c>
       <c r="F16" s="68" t="inlineStr">
         <is>
-          <t>9045 綁在機台的系統批號輸入欄，寫入即為機台批號身分。本機 SVID 1006 可讀(回目前作用中的批號)，EC 側未登錄故不可寫。⚠ 是否開放請見「Open item 9」；本機目前設定批號的唯一途徑是 RCMD SET_LOT_INFO + LOTSTART。</t>
+          <t>9045 綁在機台的系統批號輸入欄，寫入即為機台批號身分。本機 SVID 1006 可讀，EC 側未登錄故不可寫。〔20260804 第 6 版：1006 的回值定義已改變 —— 現在回「機上所有批號，以半角逗號串接」。單批時回該批號本身(與舊行為逐位元組相同)，多批時如 "LOTA,LOTB,LOTC"；批數 = 逗號數 + 1，首批 = 第一個逗號前的字串。這是下架 SVID 66030 Active Lot Count 與 66031 Current Lot ID 的替代路徑。未開批時仍回主畫面批號輸入欄的文字(未變)。詳見第 31 項。〕⚠ 是否開放請見「Open item 9」；本機目前設定批號的唯一途徑是 RCMD SET_LOT_INFO + LOTSTART。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -2428,12 +2428,12 @@
         <is>
           <t>貴端 2026-08-04 裁定：HT-160S 一律只公佈 HT-90XX 家族編號，自有段不再保留。第 5 版 追加項2 第 30 項曾主張其中八個「家族無同義號碼故必須自定義」、另兩個「因預設 Report 1 形狀已凍結故保留」—— 本版依貴端裁定全部下架，第 30 項的結論即以本項取代(該項作為當時的評估紀錄保留，不予改寫)。十個號碼與其替代路徑逐一如下：
 • 66000 Run Mode → 改用家族 SVID 1008 Run Mode(ASCII，本機恆回 "0" = Normal)。⚠ 請注意資訊落差：1008 的家族值域是「0:Normal / 1:RT / 2:EQC」(測試流程模式)，本機為分選機、無重測也無 EQC，故恆為 0；原 66000 帶的是機台任務模式(0=Normal / 1=Home / 2=OneCycle / 3=CleanOut / 4=TrayFeed)，此資訊自本版起不再由任何 SVID 公佈，請改讀 SVID 1011 Machine State 或追蹤任務類 CEID(3 / 4 按下、41 / 42 完成)。HT-90XX 亦是如此。
-• 66001 System Running → 無替代號碼。是否在運轉請由 SVID 1011 的狀態文字與 CEID 1 Start / 2 Pause 判定。HT9046LS V3.32.810 與 HT9011UC V3.33.899 皆未註冊同義 SVID。
+• 66001 System Running → 無替代號碼。是否在運轉請由 SVID 1011 的狀態文字與 Start / Pause 事件判定。⚠ Start 有兩個號碼，兩個都要訂：CEID 1 Start Pressed 只在「機內無 IC」時發，CEID 76 Start Pressed HasIC 才是「機內有 IC」時的 Start（暫停後續跑、警報解除後續跑都走 76，產線上這才是常態）；停止側為 CEID 2 Pause Pressed。只訂 CEID 1 會漏掉絕大多數的重新起動。HT9046LS V3.32.810 與 HT9011UC V3.33.899 皆未註冊同義 SVID。
 • 66002 Control State → 改讀 SVID 4 GemControlState(與 9 PreviousGemControlState)，值域為 HT9045 的 1=Off-Line / 2=On-Line Local / 3=On-Line Remote。本機內部仍以 GEM 標準值域 1/4/5 保存同一個狀態，但不再對外公佈該編號。
 • 66010 Alarm Active / 66011 Alarm Code → 無替代號碼。警報一律走 S5F1(目錄走 S5F6)，與 HT9045 相同；810 / 899 亦無任何「目前警報」SV。
 • 66020 Total IC → 改讀 SVID 1101 Loader Count(自 Loader 盤取起的 IC 數)與 SVID 1102 Output Total Count(已放入 Bin 的 IC 數)。原 66020 是本機第三個計數器(本批已處理總數)，家族無此概念。
 • 66021 Total Sorted → 改讀 SVID 1102 Output Total Count。兩者本來就綁同一個計數器(MachineRun.iTotalSorted)，值完全相同，屬純去重。
-• 66030 Active Lot Count / 66031 Current Lot ID → 改由 SVID 1006 Lot ID 承接，見第 32 項。
+• 66030 Active Lot Count / 66031 Current Lot ID → 改由 SVID 1006 Lot ID 承接，見第 32 項（⚠ 批數的導出必須先判空字串，理由見該項）。
 • 66032 Sort Mode → 無替代號碼。家族沒有分選模式 SVID(唯一近似的 35530 "[I27] Manual sort mode" 是 HT9045/46 的 BOOLEAN 機台選項，型別與語意皆不合)。⚠ 明確接受的能力損失：貴端仍可用 S2F41 LOTSTART 的 SORTMODE 參數「設定」分選模式(行為完全未變)，但自本版起無法再用 S1F3「回讀」確認；若貴端需要回讀，請配發一個家族編號給本方。
 ⚠ 這十個號碼自本版起為永久空號，本方永不挪用。舊 host 若仍綁著它們，S1F3 / 報表該格回空 list item &lt;L[0]&gt;，list 長度不變、後續欄位不位移 —— 且 &lt;L[0]&gt;(位元組 01 00)與「已註冊但字串為空」的 &lt;A[0]&gt;(位元組 41 00)在線上可區分，故這是可偵測的空白，不是無法察覺的錯值。本機共註冊 SVID 數 76 → 67。</t>
         </is>
@@ -2450,7 +2450,7 @@
           <t>貴端 2026-08-04 指定以半角逗號(,)為分隔符，不加空白。
 • 單批：回該批號本身，例如 "PROBE_LOT_A" —— 與本版之前逐位元組相同。這是刻意的：貴端持久化的 RPTID 502 第 1 格就是 1006，單批生產時貴端的解析完全不需改動。
 • 多批：依註冊順序串接，例如 "PROBE_LOT_A,PROBE_LOT_B,PROBE_LOT_C"。
-• 由此回推被下架的兩個號碼：批數 = 逗號數 + 1(原 66030)；首批 = 第一個逗號前的字串(原 66031)。
+• 由此回推被下架的兩個號碼：首批 = 第一個逗號前的字串(原 66030 的同伴 66031)；批數 = 「1006 為空字串則 0，否則逗號數 + 1」(原 66030)。⚠ **批數務必先判空字串** —— 未開批時 1006 回主畫面批號輸入欄的文字(通常為空)，此時機上其實是 0 批，直接套「逗號數 + 1」會把 0 批誤報成 1 批(已退役的 66030 在該狀態回 0)。另請注意：批號欄若有操作員打的字但尚未開批，1006 會回那串文字，那同樣是 0 批 —— 需要嚴格批數請以 LOTSTART / CLEAR_LOT_INFO 的事件流追蹤。
 • 未開批(批次登錄表為空)：回主畫面批號輸入欄當下的文字 —— 與既有公佈的契約相同，未變更。
 • 已被移除的批次會留下空槽位(其他模組持有槽位索引，故不能重排)，串接時一律跳過空槽，因此不會出現開頭逗號或連續逗號。
 ⚠ 請貴端確認兩件事：(1) 京元批號本身不含半角逗號 —— 若含，串接後無法唯一切割，請改用其他分隔符；(2) 貴端 RPTID 502 第 1 格的解析在多批生產時要能接受逗號串。型別仍為 A、報表格數與順序完全不變。</t>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F16" s="68" t="inlineStr">
         <is>
-          <t>9045 綁在機台的系統批號輸入欄，寫入即為機台批號身分。本機 SVID 1006 可讀，EC 側未登錄故不可寫。〔20260804 第 6 版：1006 的回值定義已改變 —— 現在回「機上所有批號，以半角逗號串接」。單批時回該批號本身(與舊行為逐位元組相同)，多批時如 "LOTA,LOTB,LOTC"；批數 = 逗號數 + 1，首批 = 第一個逗號前的字串。這是下架 SVID 66030 Active Lot Count 與 66031 Current Lot ID 的替代路徑。未開批時仍回主畫面批號輸入欄的文字(未變)。詳見第 31 項。〕⚠ 是否開放請見「Open item 9」；本機目前設定批號的唯一途徑是 RCMD SET_LOT_INFO + LOTSTART。</t>
+          <t>9045 綁在機台的系統批號輸入欄，寫入即為機台批號身分。本機 SVID 1006 可讀，EC 側未登錄故不可寫。〔20260804 第 6 版：1006 的回值定義已改變 —— 現在回「機上所有批號，以半角逗號串接」。單批時回該批號本身(與舊行為逐位元組相同)，多批時如 "LOTA,LOTB,LOTC"；批數 = 「空字串則 0，否則逗號數 + 1」(⚠ 必須先判空，未開批時本號回主畫面批號欄文字，那是 0 批)，首批 = 第一個逗號前的字串。這是下架 SVID 66030 Active Lot Count 與 66031 Current Lot ID 的替代路徑。未開批時仍回主畫面批號輸入欄的文字(未變)。詳見第 31 項。〕⚠ 是否開放請見「Open item 9」；本機目前設定批號的唯一途徑是 RCMD SET_LOT_INFO + LOTSTART。</t>
         </is>
       </c>
     </row>

--- a/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
+++ b/docs/SECS/SECS_GEM功能_Handler_20260804.xlsx
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B148"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="26" customWidth="1" style="62" min="1" max="1"/>
@@ -1048,7 +1048,7 @@
       <c r="B10" s="26" t="inlineStr">
         <is>
           <t>整份改為 HT9045 字典的逐字複本(1-275 全數註冊，別名與 HT9045 逐字相同)。新增「本機發射」欄：52 個號碼本機真的會送(綠底並標 ★)，其餘 223 個已註冊但無發射點、永不送出。
-〔20260804 現況：CEID 字典已於 2026-08-03「追加項3」補齊為 1-292(第 1 版為 1-275)；發射點現為 56 個無條件發射(綠底、第 3 欄標 V)＋1 個條件發射(CEID 78，標「V(條件：出廠預設關閉)」)，合計 57 個，其餘 235 個已註冊但永不送出(第 3 欄標「—」)。本檔 CEID 工作表即為此數。⚠ 第 3 欄的欄名自 20260804 起為「HT-160」(原「本機發射」)，標記由「★」改為「V」—— 只是樣式，集合與底色完全未變。〕</t>
+〔20260804 現況：CEID 字典已於 2026-08-03「追加項3」補齊為 1-292(第 1 版為 1-275)；發射點現為 55 個無條件發射(綠底、第 3 欄標 V)＋1 個條件發射(CEID 78，標「V(條件：出廠預設關閉)」)，合計 56 個，其餘 236 個已註冊但永不送出(第 3 欄標「—」)。本檔 CEID 工作表即為此數。⚠ 第 3 欄的欄名自 20260804 起為「HT-160」(原「本機發射」)，標記由「★」改為「V」—— 只是樣式，集合與底色完全未變。⚠ 20260804 追加項4：CEID 17 Enter Tool Page 已由 V 改為「—」(主畫面 Tools 鍵移除、失去唯一發射點)，故無條件發射由 56 減為 55、合計由 57 減為 56、未發射由 235 增為 236，見第 35 項。〕</t>
         </is>
       </c>
     </row>
@@ -2609,6 +2609,68 @@
       <c r="B148" s="51" t="inlineStr">
         <is>
           <t>以 openpyxl 對第 6 版(commit 871bf08)逐格比對：差異共 59 格，全部落在 CEID!B1 / C1 / C 欄的 56 個發射標記，以及 ECID!C2 欄頭，無任何一格改到號碼、名稱、Report、備註或發射集合。CEID 表發射標記統計實測：V 56 個、V(條件：…) 1 個、— 235 個，合計 292。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-04 第 6 版 追加項4(同日，承第 6 版)</t>
+        </is>
+      </c>
+      <c r="B150" s="40" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="34" t="inlineStr">
+        <is>
+          <t>依據韌體 Firmware</t>
+        </is>
+      </c>
+      <c r="B151" s="51" t="inlineStr">
+        <is>
+          <t>HT-160S 1.0.0.0, branch feat/iosetview-172-refactor (commit 1f17067)。本追加項為程式碼變更：移除主畫面工具列的 Tools 鍵，並修正 Message 鍵誤接警報視窗。建置：模擬版 -Clean exit 0；註銷 SOFT_SIMULATE 之真機版 -Full exit 0；還原後再 -Full exit 0；原始碼編碼檢查 166 檔通過。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="34" t="inlineStr">
+        <is>
+          <t>⚠ 35. CEID 17 Enter Tool Page 自本版起不再發射(主畫面 Tools 鍵已移除)</t>
+        </is>
+      </c>
+      <c r="B152" s="51" t="inlineStr">
+        <is>
+          <t>本機主畫面工具列原有一顆 Tools 鍵，CEID 17 的唯一發射點就是它的按鈕處理常式。該鍵打開的是一片完全空白的視窗 —— HT-90XX 的 Tool 頁(使用者權限設定、警報碼產生)在本機分屬 UserRoleManager 與其他模組，從未移植過來，因此本日已將該按鈕整顆移除，其右側各鍵依序左移。
+• CEID 17 自本版起改列「已註冊但永不送出」：號碼與名稱仍保留在字典內(S1F23 / S1F24 全查仍會回它)，S2F35 連結仍會被接受(DRACK=0x00)，但永遠不會有 S6F11 送出。貴端若有訂閱請移除。
+• 無條件發射點由 56 減為 55，加上 CEID 78 的條件發射，合計由 57 減為 56；「已註冊但永不送出」由 235 增為 236。292 個號碼的總數不變。
+• 同時修正一個相關缺陷(不影響 SECS 介面)：Message 鍵原本開啟的是警報/回復視窗而非資料頁。在沒有警報時開啟該視窗會鳴警報蜂鳴器、把實體操作面板的按鍵交由該視窗處理，且面板 PAUSE 鍵會直接停下所有馬達。該鍵已改指向資料頁(目前為保留頁)。CEID 22 Enter Message Page 的發射時機不變 —— 仍是操作員按下 Message 鍵時送出，故 22 仍在發射清單內。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="34" t="inlineStr">
+        <is>
+          <t>本次未變動 Unchanged</t>
+        </is>
+      </c>
+      <c r="B153" s="51" t="inlineStr">
+        <is>
+          <t>除 CEID 17 之外，其餘 291 個號碼的編號、名稱、語意與發射時機全部未變；SVID / ECID 的號碼、名稱、型別、可寫範圍未變；預設 Report 1(僅 1027 System Time)與 Report 2-7 未變；272-275 的 AMR 交握形狀未變；S5 警報目錄(481 筆)未變；Soter 輸出檔契約未變。本追加項只移除一顆從未有實際內容的操作介面按鈕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="34" t="inlineStr">
+        <is>
+          <t>追加項4 的驗證 Verification</t>
+        </is>
+      </c>
+      <c r="B154" s="51" t="inlineStr">
+        <is>
+          <t>1. 建置：模擬版 -Clean exit 0；註銷 SOFT_SIMULATE 之真機版 -Full exit 0；還原 SOFT_SIMULATE 後再 -Full exit 0；scripts/ops/check-ht160s-source-encoding.ps1 通過(166 檔)。
+2. 啟動實測：實際啟動重新建置的 EXE\ht160s.exe，各頁自我檢測回報 OPENED=Language,Product,Maintance,Teach,MotorTest,Offset,Speed,Message,Note，無例外；主畫面截圖確認工具列為 Language / Product / Maintance / Offset / Speed / Message / Monitor / Exit 共 8 鍵，Tools 已消失且無空位。
+3. 本表統計實測：CEID 工作表 V 55 個、V(條件：…) 1 個、— 236 個，合計 292。
+4. 規格書 HT160S_SECS_Interface_Spec_20260727.md / .html 已同步：§3.3.1 由 57 減為 56 並移除 CEID 17 一列，§3.3.2 由 235 增為 236 並新增 CEID 17 的逐條說明。</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2919,7 @@
   &lt;L [0] 
   &gt;
 .
-[20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 292 個 CEID(與貴端現場機台的字典逐筆相同，含本機已註冊但不發射的 235 個)〔20260803:由 275 補齊為 292，見「第 4 版 追加項3」〕；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。</t>
+[20260730] 已實作(2026-07-30 新增)。S1F23 -&gt; S1F24 回 L,n{L,3{U4 CEID, A CENAME, L,m{U4 VID}}}。&lt;L[0]&gt; 全查回全部 292 個 CEID(與貴端現場機台的字典逐筆相同，含本機已註冊但不發射的 236 個)〔20260803:由 275 補齊為 292，見「第 4 版 追加項3」〕；指定 CEID 只回該幾筆；未註冊的 CEID 回 {CEID, '', L,0}(與 HT9045 同)。VID 清單由該 CEID 所連結的報表依序展開，順序與該事件 S6F11 內的排列一致，重複的 VID 不去除(一個 CEID 連兩張含相同 SVID 的報表時，S6F11 本來就會送兩次)。註：本訊息只是字典查詢，不等於訂閱 — 實際要收哪些事件仍由 S2F33 / S2F35 / S2F37 決定。</t>
         </is>
       </c>
     </row>
@@ -5173,27 +5235,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="67" t="n">
+      <c r="A18" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="70" t="inlineStr">
         <is>
           <t>Enter Tool Page</t>
         </is>
       </c>
-      <c r="C18" s="67" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D18" s="68" t="inlineStr">
-        <is>
-          <t>Report 1</t>
-        </is>
-      </c>
-      <c r="E18" s="68" t="inlineStr">
-        <is>
-          <t>進入 Tool 頁</t>
+      <c r="C18" s="69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="n"/>
+      <c r="E18" s="70" t="inlineStr">
+        <is>
+          <t>HT-160S 無 Tool 頁 —— 主畫面工具列的 Tools 鍵只會開出一片空白視窗，2026-08-04 已連同按鈕移除，本號碼自此不再發射(見「修訂說明」第 35 項)</t>
         </is>
       </c>
     </row>
